--- a/docs/SEM_FIBSEM_TAPP_v4.xlsx
+++ b/docs/SEM_FIBSEM_TAPP_v4.xlsx
@@ -1,30 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubC\USGIN\geochemBuildingBlocks\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D001EC80-D583-40EB-8994-9C69A560FDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CFFD98-C578-47BA-AA64-80A3DF6BF1DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="189" yWindow="2049" windowWidth="21848" windowHeight="9951" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1995" yWindow="1680" windowWidth="25065" windowHeight="14775" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAPP" sheetId="1" r:id="rId1"/>
     <sheet name="Legends" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TAPP!$C$1:$M$53</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="542">
   <si>
     <t>Metadata Item</t>
   </si>
@@ -209,6 +206,9 @@
     <t>match. methodDefinition.schema:name is the short descriptive name for the method.</t>
   </si>
   <si>
+    <t xml:space="preserve">readOnly: True </t>
+  </si>
+  <si>
     <t>Technique</t>
   </si>
   <si>
@@ -359,6 +359,10 @@
     <t>match. schema:funding[] is an array of MonetaryGrant; also has schema:identifier (award number) and schema:funder (organisation).</t>
   </si>
   <si>
+    <t xml:space="preserve">put text in MonetaryGrant name unless can clearly parse identifier distinct from name. 
+readOnly: True </t>
+  </si>
+  <si>
     <t>Protocol Reference(s)</t>
   </si>
   <si>
@@ -374,6 +378,10 @@
     <t>match. schema:relatedLink[] is a labeledLink with schema:url and schema:name; fits DOIs/URLs of method publications.</t>
   </si>
   <si>
+    <t xml:space="preserve">target URL to publication , target name should be title of publication 
+readOnly: True </t>
+  </si>
+  <si>
     <t>Protocol DOI</t>
   </si>
   <si>
@@ -386,6 +394,15 @@
     <t>e.g., 'https://doi.org/10.xxxxx/protocol-id' | 'pending'</t>
   </si>
   <si>
+    <t>$Dataset.schema:measuremntTechnique.schema:DefinedTerm.schema.name and schema.identifier</t>
+  </si>
+  <si>
+    <t>This should be the identifier for the protocol definition that the analysis level 'detail' is extenting for a particular dataset.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
     <t>Analyst</t>
   </si>
   <si>
@@ -396,6 +413,9 @@
   </si>
   <si>
     <t>$Dataset.prov:wasGeneratedBy.schema:Agent/schema:Person.schema:name, schema:identifier</t>
+  </si>
+  <si>
+    <t>optional</t>
   </si>
   <si>
     <t>Analysis Start Date</t>
@@ -609,6 +629,11 @@
     <t>match. schema:object[] is an array of DefinedTerm or string describing target material (mineral phase, glass, oxide, etc.). Need vocabulary or target materials…</t>
   </si>
   <si>
+    <t xml:space="preserve">schema:DefinedTerm.schema:termCode
+datatype: enum {Silicate glass | Feldspar | Pyroxene | Olivine | Oxide | Sulfide | Carbonate | Phosphate | Native metal | Iron meteorite | Fluid inclusion | Melt inclusion | Whole rock | Other: specify} 
+readOnly: True </t>
+  </si>
+  <si>
     <t>Carbonaceous nanoglobules, Tagish Lake (C2) meteorite (HCl/HF acid residue concentrate)</t>
   </si>
   <si>
@@ -663,852 +688,10 @@
     <t>2026-05-22</t>
   </si>
   <si>
+    <t>$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation']</t>
+  </si>
+  <si>
     <t>Sample preparation is a dedicated step (typically schema:position=1) in the actionProcess; schema:object is input, mostly likely the original sample. Schema:result is the product that will be used directly for analysis, e.g. polished thin section or epoxy mount; describe procedure in schema:step/schema:description</t>
-  </si>
-  <si>
-    <t>HCl and HF acid dissolution residue from pristine Tagish Lake pieces; deposited on lacey C TEM grid attached to Al-SEM stub; uncoated</t>
-  </si>
-  <si>
-    <t>Carbon-coated polished thin sections; high vacuum analysis</t>
-  </si>
-  <si>
-    <t>Small coal pillars (~2 mm diameter, 2 mm height) drilled orthogonal to bedding; polished with cross section polisher to remove ~1-2 µm oxide layer; no coating applied</t>
-  </si>
-  <si>
-    <t>Bulk coal polished to ~10 mm × 2-3 mm using polishing and burnishing machine; further polished with cross section polisher; thin gold coating applied by sputtering</t>
-  </si>
-  <si>
-    <t>Polished thin section (section 126A prepared from Grain 126); no coating or SEM-specific preparation stated</t>
-  </si>
-  <si>
-    <t>Polished thin section (section 126A prepared from Grain 126); no coating or EBSD-specific preparation stated</t>
-  </si>
-  <si>
-    <t>Embedded in epoxy, polished to ¼ µm level, sputtered with 30-nm-thick carbon film</t>
-  </si>
-  <si>
-    <t>Cuboidal samples (~0.5×1×1 cm) polished with dry emery paper and argon ion polishing; high-pressure freezing and freeze-drying; glued onto sample holder</t>
-  </si>
-  <si>
-    <t>Attached to Al cylinder SEM mount with double-sided C tape; sputter coated with ~5 nm carbon</t>
-  </si>
-  <si>
-    <t>Polished sections; coated with 0.1 nm carbon for charge mitigation</t>
-  </si>
-  <si>
-    <t>Sections extracted from fine-grained matrix areas in polished sections; BSE and SE images acquired before and after sectioning</t>
-  </si>
-  <si>
-    <t>Particles placed on PELCO carbon conductive tabs on Al SEM round; no protective coating stated</t>
-  </si>
-  <si>
-    <t>Particles dispersed on conductive carbon dots on Al SEM pin mounts</t>
-  </si>
-  <si>
-    <t>Polished thin sections; ~100 nm graphite coating (as stated in CL emitting volume calculation)</t>
-  </si>
-  <si>
-    <t>Sample Name</t>
-  </si>
-  <si>
-    <t>Name or identifier of the sample or sample mount analyzed in this session.</t>
-  </si>
-  <si>
-    <t>e.g., 'Bennu OREX-800045-103' | 'NWA 8657 polished thin section 1'</t>
-  </si>
-  <si>
-    <t>$Dataset.prov:wasGeneratedBy.schema:object[@type ="schema:Thing",            "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:name</t>
-  </si>
-  <si>
-    <t>Section 126A (USNM 7908)</t>
-  </si>
-  <si>
-    <t>NWA 7317</t>
-  </si>
-  <si>
-    <t>SC; HBC</t>
-  </si>
-  <si>
-    <t>OREX-501018-100</t>
-  </si>
-  <si>
-    <t>Sample Persistent Identifier</t>
-  </si>
-  <si>
-    <t>Persistent identifier (e.g., IGSN) for the sample analyzed.</t>
-  </si>
-  <si>
-    <t>URI / IGSN</t>
-  </si>
-  <si>
-    <t>e.g., 'IGSN:AU1234567'</t>
-  </si>
-  <si>
-    <t>$Dataset.prov:wasGeneratedBy.schema:object[@type = "schema:Thing",  "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:identifier</t>
-  </si>
-  <si>
-    <t>USNM 7908 (section 126A)</t>
-  </si>
-  <si>
-    <t>3. Instrument &amp; Software</t>
-  </si>
-  <si>
-    <t>Instrument Manufacturer</t>
-  </si>
-  <si>
-    <t>Make of the SEM or FIB-SEM instrument.</t>
-  </si>
-  <si>
-    <t>JEOL | Zeiss | FEI / Thermo Fisher Scientific | Hitachi | Tescan | Phenom | Other: specify | Unknown | N/A | None</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:instrument.schema:manufacturer.schema:Organization.schema:name</t>
-  </si>
-  <si>
-    <t>match. CDIF instrument inherits schema.org Product's schema:manufacturer.</t>
-  </si>
-  <si>
-    <t>FEI</t>
-  </si>
-  <si>
-    <t>Zeiss</t>
-  </si>
-  <si>
-    <t>JEOL</t>
-  </si>
-  <si>
-    <t>Hitachi</t>
-  </si>
-  <si>
-    <t>Other: Leo Electron Microscopy (now Zeiss)</t>
-  </si>
-  <si>
-    <t>Carl Zeiss</t>
-  </si>
-  <si>
-    <t>FEI Company, USA</t>
-  </si>
-  <si>
-    <t>ZEISS (Carl Zeiss)</t>
-  </si>
-  <si>
-    <t>FEI (now Thermo Fisher Scientific)</t>
-  </si>
-  <si>
-    <t>Thermo Fisher Scientific (ThermoScientific)</t>
-  </si>
-  <si>
-    <t>Instrument Model</t>
-  </si>
-  <si>
-    <t>Model designation of the SEM or FIB-SEM instrument, including generation suffix if applicable.</t>
-  </si>
-  <si>
-    <t>e.g., 'JEOL JSM-7600F' | 'Zeiss Supra 55 FEG-SEM' | 'FEI Quanta 650 FEG' | 'Thermo Fisher Quattro S' | 'FEI Helios NanoLab 660' | 'Zeiss Crossbeam 540'</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:instrument.schema:model.schema:name</t>
-  </si>
-  <si>
-    <t>match. CDIF instrument inherits schema.org Product's schema:model.</t>
-  </si>
-  <si>
-    <t>Nova 200 NanoLab DualBeam</t>
-  </si>
-  <si>
-    <t>ZEISS 1550VP</t>
-  </si>
-  <si>
-    <t>JSM-5410LV</t>
-  </si>
-  <si>
-    <t>S-2500C</t>
-  </si>
-  <si>
-    <t>Leo 440</t>
-  </si>
-  <si>
-    <t>Leo 1540 FIB/SEM CrossBeam</t>
-  </si>
-  <si>
-    <t>Crossbeam 540</t>
-  </si>
-  <si>
-    <t>Quanta 250</t>
-  </si>
-  <si>
-    <t>SUPRA 55</t>
-  </si>
-  <si>
-    <t>1550VP</t>
-  </si>
-  <si>
-    <t>Supra 40</t>
-  </si>
-  <si>
-    <t>Helios NanoLab 650</t>
-  </si>
-  <si>
-    <t>7600F</t>
-  </si>
-  <si>
-    <t>S-4800</t>
-  </si>
-  <si>
-    <t>Helios G3</t>
-  </si>
-  <si>
-    <t>Helios G4 UX</t>
-  </si>
-  <si>
-    <t>Quanta 3D 600</t>
-  </si>
-  <si>
-    <t>JSM-7000F</t>
-  </si>
-  <si>
-    <t>Electron Source</t>
-  </si>
-  <si>
-    <t>Type of electron gun used in the SEM instrument.</t>
-  </si>
-  <si>
-    <t>Cold-FEG | Schottky FEG | LaB6 / CeB6 | Tungsten (W) | Other: specify | Unknown | N/A | None</t>
-  </si>
-  <si>
-    <t>match. Electron source/gun modelled as a sub-component of the instrument via schema:hasPart[]; classify the part via schema:additionalType (e.g. 'ElectronGun:FEG') and carry the label in schema:name.</t>
-  </si>
-  <si>
-    <t>Other: FEG (type not specified in paper)</t>
-  </si>
-  <si>
-    <t>Tungsten (W)</t>
-  </si>
-  <si>
-    <t>Other: FEG (type not specified)</t>
-  </si>
-  <si>
-    <t>Field emission gun (FEG)</t>
-  </si>
-  <si>
-    <t>Cold field emission gun (cold FEG)</t>
-  </si>
-  <si>
-    <t>Instrument Variant</t>
-  </si>
-  <si>
-    <t>Broad platform type of the instrument. 'Standard SEM': dedicated electron-only SEM column. 'FIB-SEM dual-beam': combined focused ion beam and SEM columns (enables TEM specimen preparation, 3D serial sectioning, ion-beam milling). 'VP-SEM / ESEM': variable-pressure or environmental SEM for imaging uncoated, hydrated, or charging specimens. An instrument may combine categories (e.g., FIB-SEM with VP capability).</t>
-  </si>
-  <si>
-    <t>Standard SEM | FIB-SEM dual-beam | VP-SEM / ESEM | FIB-SEM dual-beam + VP | Other: specify | N/A | None</t>
-  </si>
-  <si>
-    <t>FIB-SEM dual-beam</t>
-  </si>
-  <si>
-    <t>VP-SEM / ESEM</t>
-  </si>
-  <si>
-    <t>Standard SEM</t>
-  </si>
-  <si>
-    <t>ESEM (Environmental SEM)</t>
-  </si>
-  <si>
-    <t>FESEM (Field Emission SEM)</t>
-  </si>
-  <si>
-    <t>VP (Variable Pressure)</t>
-  </si>
-  <si>
-    <t>Dual Beam (FIB-SEM)</t>
-  </si>
-  <si>
-    <t>Ion Beam Source</t>
-  </si>
-  <si>
-    <t>Ion beam source type in a FIB-SEM dual-beam system. Gallium LMIS (Ga+) is the most common ion source; xenon plasma FIB (PFIB) provides higher material removal rates for large-volume milling; helium and neon ion microscopes (GFIS) provide nanometre-resolution imaging and low-damage milling.</t>
-  </si>
-  <si>
-    <t>Gallium LMIS (Ga+) | Xenon plasma FIB (PFIB) | Helium GFIS | Neon GFIS | Other: specify | N/A | None</t>
-  </si>
-  <si>
-    <t>FIB-SEM specific</t>
-  </si>
-  <si>
-    <t>Gallium LMIS (Ga+)</t>
-  </si>
-  <si>
-    <t>Gallium (Ga+) ion beam</t>
-  </si>
-  <si>
-    <t>SE Detector Type</t>
-  </si>
-  <si>
-    <t>Type of secondary electron detector used. Everhart-Thornley (ET) detector is the standard off-axis collector sensitive to SE2 and some BSE; in-lens (TLD) detectors collect high-resolution SE1 signal at short working distances; GSED/ESED detectors operate in VP/ESEM mode by using the chamber gas as the signal amplification medium.</t>
-  </si>
-  <si>
-    <t>Everhart-Thornley (ET) | In-lens / TLD (through-the-lens) | GSED (VP/ESEM) | ESED (VP/ESEM) | Other: specify | N/A | None</t>
-  </si>
-  <si>
-    <t>In-lens / TLD (through-the-lens)</t>
-  </si>
-  <si>
-    <t>BSE Detector Type</t>
-  </si>
-  <si>
-    <t>Type of backscattered electron detector. Solid-state diode detectors (single or segmented) are standard; YAG scintillator detectors offer high sensitivity at low voltage. Segmented detectors can operate in composition mode (segments summed) or topography mode (differential signal between segments). In-lens BSE detectors provide improved BSE collection at short working distances.</t>
-  </si>
-  <si>
-    <t>Solid-state diode (single) | Solid-state diode (segmented, composition mode) | Solid-state diode (segmented, topography mode) | In-lens BSE | YAG scintillator | Other: specify | N/A | None</t>
-  </si>
-  <si>
-    <t>Solid-state BSE detector</t>
-  </si>
-  <si>
-    <t>Quadrant Backscatter Detector (QBSD)</t>
-  </si>
-  <si>
-    <t>Acquisition Software</t>
-  </si>
-  <si>
-    <t>Software used to control the SEM and acquire data, including version number. For FIB-SEM 3D tomography, include the automated slice-and-view module name and version.</t>
-  </si>
-  <si>
-    <t>e.g., 'JEOL Analysis Station v3.5' | 'Oxford AZtec 6.0' | 'Zeiss SmartSEM 6.06' | 'Thermo Fisher Auto Slice and View G4 (3D tomography)'</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.bios:computationalTool[]</t>
-  </si>
-  <si>
-    <t>match. bios:computationalTool[] with ada:toolRole='acquisition' captures the acquisition/automation software; schema:name, schema:version, and schema:url are siblings.</t>
-  </si>
-  <si>
-    <t>toolRole = acquisition</t>
-  </si>
-  <si>
-    <t>Gatan DigitalMicrograph (CL image assembly)</t>
-  </si>
-  <si>
-    <t>Oxford INCA Energy</t>
-  </si>
-  <si>
-    <t>Oxford AZtec (Point &amp; ID programme)</t>
-  </si>
-  <si>
-    <t>Oxford Instruments Aztec Live/x-stream</t>
-  </si>
-  <si>
-    <t>Data Reduction Software</t>
-  </si>
-  <si>
-    <t>Software used for post-acquisition data reduction and analysis. List all packages with version numbers.</t>
-  </si>
-  <si>
-    <t>e.g., 'Oxford AZtec 6.0 (EDS quantification); Oxford AZtec Crystal 2.1 (EBSD); Gatan DigitalMicrograph 3.5 (CL); FIJI 2.15 (image processing); Avizo 2023 (3D segmentation)'</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>toolRole = data reduction</t>
-  </si>
-  <si>
-    <t>Gatan DigitalMicrograph</t>
-  </si>
-  <si>
-    <t>Avizo 7 (3D digital core software); Multiple-point geostatistics for pore network model</t>
-  </si>
-  <si>
-    <t>Oxford INCA Energy (semi-quantitative phase determination from atomic proportions)</t>
-  </si>
-  <si>
-    <t>Fiji/ImageJ (StackReg/TurboReg for slice alignment; VolumeJ for volume rendering); Adobe Photoshop CS6 (image enhancement); FEI Avizo Fire 8.1.1 (pore volume reconstruction and segmentation)</t>
-  </si>
-  <si>
-    <t>Oxford AZtec</t>
-  </si>
-  <si>
-    <t>Oxford Instruments Aztec</t>
-  </si>
-  <si>
-    <t>4. Measurement Information</t>
-  </si>
-  <si>
-    <t>Analytical Mode</t>
-  </si>
-  <si>
-    <t>Primary analytical mode(s) executed under this protocol. For multi-mode protocols (e.g., simultaneous BSE + EDS mapping), list all active modes.</t>
-  </si>
-  <si>
-    <t>SE Imaging | BSE Imaging | EDS | SEM-WDS | CL | EBSD | TEM Sample Preparation | 3D Tomography | Multiple (specify) | Other: specify | N/A | None</t>
-  </si>
-  <si>
-    <t>SE Imaging</t>
-  </si>
-  <si>
-    <t>BSE Imaging</t>
-  </si>
-  <si>
-    <t>EDS</t>
-  </si>
-  <si>
-    <t>EBSD</t>
-  </si>
-  <si>
-    <t>CL</t>
-  </si>
-  <si>
-    <t>BSE (QBSD mode)</t>
-  </si>
-  <si>
-    <t>Spot analysis</t>
-  </si>
-  <si>
-    <t>Element mapping</t>
-  </si>
-  <si>
-    <t>Sequential FIB-SEM tomography (serial cross-section imaging)</t>
-  </si>
-  <si>
-    <t>Low-angle backscattered electron (BSE) imaging</t>
-  </si>
-  <si>
-    <t>Point spectra (spot analysis, Point &amp; ID)</t>
-  </si>
-  <si>
-    <t>EDS mapping</t>
-  </si>
-  <si>
-    <t>In-situ FIB lift-out; cross-section lamella preparation for TEM</t>
-  </si>
-  <si>
-    <t>In-situ FIB lift-out; lamella preparation for XANES and TEM</t>
-  </si>
-  <si>
-    <t>In-situ FIB lift-out; cross-section lamella preparation</t>
-  </si>
-  <si>
-    <t>Panchromatic CL imaging; hyperspectral CL; monochromatic CL imaging</t>
-  </si>
-  <si>
-    <t>Elemental maps and spot spectra (SEM-EDX) for presolar grain phase identification</t>
-  </si>
-  <si>
-    <t>Accelerating Voltage</t>
-  </si>
-  <si>
-    <t>Electron beam accelerating voltage in kilovolts. Affects X-ray generation depth (EDS/WDS), EBSD pattern quality, imaging resolution, and beam penetration. Low voltages (1-5 kV) improve surface sensitivity and reduce beam damage; high voltages (15-20 kV) improve X-ray generation for quantitative analysis.</t>
-  </si>
-  <si>
-    <t>Numeric (kV)</t>
-  </si>
-  <si>
-    <t>e.g., 2 | 5 | 10 | 15 | 20</t>
-  </si>
-  <si>
-    <t>500 V; 1 kV; 5 kV</t>
-  </si>
-  <si>
-    <t>10 kV</t>
-  </si>
-  <si>
-    <t>20 kV</t>
-  </si>
-  <si>
-    <t>15 kV</t>
-  </si>
-  <si>
-    <t>15–20 kV</t>
-  </si>
-  <si>
-    <t>2 kV (SEM imaging)</t>
-  </si>
-  <si>
-    <t>30 keV (FIB milling and thinning)</t>
-  </si>
-  <si>
-    <t>16 to 30 keV (coarse milling); down to 1 keV (polishing)</t>
-  </si>
-  <si>
-    <t>30 kV (initial milling); 16 kV (intermediate); 5 kV (final thinning)</t>
-  </si>
-  <si>
-    <t>5 keV</t>
-  </si>
-  <si>
-    <t>Beam Current</t>
-  </si>
-  <si>
-    <t>Electron beam probe current. Higher current improves signal-to-noise for X-ray analysis (EDS/WDS, EBSD) and CL but may increase beam damage and reduce spatial resolution. Express in nA; for sub-nA values use decimal notation (e.g., 0.4 nA).</t>
-  </si>
-  <si>
-    <t>Numeric (nA)</t>
-  </si>
-  <si>
-    <t>e.g., 0.4 | 0.9 | 2 | 5 | 10 | 20</t>
-  </si>
-  <si>
-    <t>Analyte-Specific for SEM-WDS</t>
-  </si>
-  <si>
-    <t>70 fA (500 V); 1.4 pA (1 kV); 98 pA (5 kV)</t>
-  </si>
-  <si>
-    <t>6 nA</t>
-  </si>
-  <si>
-    <t>2.0 nA</t>
-  </si>
-  <si>
-    <t>~900 pA</t>
-  </si>
-  <si>
-    <t>0.8 to 2.5 nA (thinning)</t>
-  </si>
-  <si>
-    <t>1 to 4 nA</t>
-  </si>
-  <si>
-    <t>Working Distance</t>
-  </si>
-  <si>
-    <t>Distance between the objective lens pole piece and the specimen surface in millimetres. Affects spatial resolution, depth of focus, EDS X-ray take-off angle, and EBSD geometry.</t>
-  </si>
-  <si>
-    <t>Numeric (mm)</t>
-  </si>
-  <si>
-    <t>e.g., 4 | 8 | 10 | 15</t>
-  </si>
-  <si>
-    <t>0.5–5.4 mm</t>
-  </si>
-  <si>
-    <t>5.4 mm (eucentric height for electron and ion columns)</t>
-  </si>
-  <si>
-    <t>~10 mm</t>
-  </si>
-  <si>
-    <t>8 mm</t>
-  </si>
-  <si>
-    <t>4 mm</t>
-  </si>
-  <si>
-    <t>Dwell Time per Pixel</t>
-  </si>
-  <si>
-    <t>Time the electron beam dwells on each pixel during raster scanning (imaging modes) or on each step position during compositional mapping (EDS and WDS mapping modes), in microseconds or milliseconds. Longer dwell time improves signal-to-noise and counting statistics but increases total dose and can cause beam damage or contamination on sensitive materials. For WDS mapping, the dwell time is per spectrometer per pixel.</t>
-  </si>
-  <si>
-    <t>Numeric + unit</t>
-  </si>
-  <si>
-    <t>e.g., '400 ns' | '10 µs' | '1 ms'</t>
-  </si>
-  <si>
-    <t>Protective Coating Deposition</t>
-  </si>
-  <si>
-    <t>Type and deposition conditions of the protective coating applied to the sample surface before FIB milling. E-beam deposition causes less surface damage than ion-beam deposition and should be applied as the initial layer. Typical coatings: platinum (Pt) or carbon (C). State material, deposition method, beam conditions, and approximate thickness.</t>
-  </si>
-  <si>
-    <t>e.g., 'E-beam Pt (5 kV, 1.5 nA, ~500 nm) then Ga+ ion-beam Pt (30 kV, 0.3 nA, ~2 µm)' | 'E-beam C (5 kV) + ion-beam C (2-3 µm total)'</t>
-  </si>
-  <si>
-    <t>No coating applied; not sputtered with gold or other materials</t>
-  </si>
-  <si>
-    <t>12-µm wide × 4-µm tall carbon capping layer deposited on matrix areas</t>
-  </si>
-  <si>
-    <t>Electron-beam deposited carbon (~0.5–1 µm); followed by ion beam-deposited carbon (~2–3 µm capping layer)</t>
-  </si>
-  <si>
-    <t>Coarse Milling Conditions</t>
-  </si>
-  <si>
-    <t>Ion beam voltage and current used for bulk material removal during FIB milling. For TEM specimen preparation: bulk trenching to isolate the lamella and intermediate thinning. For 3D tomography: face preparation and initial slice removal.</t>
-  </si>
-  <si>
-    <t>e.g., '30 kV, 2.5 nA (bulk trenching); 16 kV, 0.8 nA (intermediate thinning)'</t>
-  </si>
-  <si>
-    <t>30 kV, 10 pA Ga beam</t>
-  </si>
-  <si>
-    <t>Standard stair step; 30 keV, currents 2.5 to 0.8 nA</t>
-  </si>
-  <si>
-    <t>Ga+ ion beam at 16–30 keV (coarse milling)</t>
-  </si>
-  <si>
-    <t>Ga+ ion beam at 30 kV (initial milling); 16 kV (intermediate)</t>
-  </si>
-  <si>
-    <t>Fine Polishing Conditions</t>
-  </si>
-  <si>
-    <t>Ion beam voltage and current for final thinning and surface polishing of the TEM lamella. Low-voltage polishing (2 kV or below) minimises Ga implantation depth, surface amorphisation, and curtaining artifacts.</t>
-  </si>
-  <si>
-    <t>e.g., '5 kV, 0.3 nA; final polish: 2 kV, 72 pA' | '1 kV, 0.1 nA final step'</t>
-  </si>
-  <si>
-    <t>FIB-SEM specific; TEM Sample Preparation specific</t>
-  </si>
-  <si>
-    <t>Various voltages down to 1 keV (polishing)</t>
-  </si>
-  <si>
-    <t>Ga+ ion beam at 5 kV (final thinning) until ~100 nm thick</t>
-  </si>
-  <si>
-    <t>Target Foil Thickness</t>
-  </si>
-  <si>
-    <t>Target thickness of the electron-transparent TEM lamella after final FIB polishing, in nanometres. Actual thickness may differ from target. Typical range: 50-150 nm for standard TEM/STEM; 200-600 nm for XANES or tomography sections.</t>
-  </si>
-  <si>
-    <t>e.g., '~100 nm' | '50-80 nm' | '100-200 nm'</t>
-  </si>
-  <si>
-    <t>&lt;100 to 600 nm (variable, depending on targeted experiment)</t>
-  </si>
-  <si>
-    <t>~100 nm</t>
-  </si>
-  <si>
-    <t>Lift-out Method</t>
-  </si>
-  <si>
-    <t>Method used to transfer the FIB-prepared lamella to the TEM support grid. In-situ lift-out uses a micromanipulator inside the FIB-SEM chamber and is the standard method for small or precious specimens.</t>
-  </si>
-  <si>
-    <t>In-situ (micromanipulator, Cu or Mo TEM half-grid) | Ex-situ | Other: specify | N/A | None</t>
-  </si>
-  <si>
-    <t>In-situ lift-out (standard stair step)</t>
-  </si>
-  <si>
-    <t>In-situ lift-out; ion beam-deposited Pt weld to Cu half grids</t>
-  </si>
-  <si>
-    <t>Ion Milling Conditions (3D Tomography)</t>
-  </si>
-  <si>
-    <t>Ion beam voltage and current used to mill each slice during FIB-SEM serial sectioning. These parameters determine material removal rate per slice and exposed surface quality.</t>
-  </si>
-  <si>
-    <t>e.g., 'Ga+ 30 kV, 2.5 nA (slice milling)'</t>
-  </si>
-  <si>
-    <t>FIB-SEM specific; 3D Tomography specific</t>
-  </si>
-  <si>
-    <t>Slice Thickness</t>
-  </si>
-  <si>
-    <t>Thickness of each FIB-milled slice during serial sectioning in nanometres. Controls the Z-axis resolution of the 3D reconstruction.</t>
-  </si>
-  <si>
-    <t>Numeric (nm)</t>
-  </si>
-  <si>
-    <t>e.g., 10 | 20 | 50 | 100</t>
-  </si>
-  <si>
-    <t>15 nm (single layer scanning thickness = 9.0 µm total / 600 slices)</t>
-  </si>
-  <si>
-    <t>Voxel Size and Image Stack Dimensions</t>
-  </si>
-  <si>
-    <t>X, Y, Z dimensions of the reconstructed 3D voxel in nanometres (X-Y pixel size from SEM image calibration; Z from slice thickness), and the total number of slices in the stack. Determined at analysis time.</t>
-  </si>
-  <si>
-    <t>e.g., '14.6 x 8.3 x 10.0 nm, 600 slices' | '14.8 x 14.8 x 20 nm, 800 slices'</t>
-  </si>
-  <si>
-    <t>9.8 × 9.8 × 15 nm voxel size; 600 slices; 7.8 × 7.8 µm scanning area; 9.0 µm total thickness</t>
-  </si>
-  <si>
-    <t>14.8×14.8 nm pixel size (XY); ~800 total slices; sub-volumes: SC=5.609×3.08×5.446 µm; HBC=4.679×3.2×4.24 µm; SEM image resolution 2.5 nm</t>
-  </si>
-  <si>
-    <t>5. Data Processing</t>
-  </si>
-  <si>
-    <t>3D Image Registration</t>
-  </si>
-  <si>
-    <t>Method used to align consecutive SEM image slices in the 3D stack to correct for drift, vibration, and curtaining artifacts. Include software used.</t>
-  </si>
-  <si>
-    <t>e.g., 'Cross-correlation (FIJI/ImageJ)' | 'Fiducial marker alignment' | 'Auto Slice and View G3 built-in drift correction' | 'Avizo drift correction'</t>
-  </si>
-  <si>
-    <t>Fiji/ImageJ StackReg and TurboReg plugins used for slice realignment</t>
-  </si>
-  <si>
-    <t>3D Segmentation Method</t>
-  </si>
-  <si>
-    <t>Method and software used to segment phases and features in the aligned 3D image stack, transforming the grayscale stack into labelled 3D regions (pores, mineral phases, grain boundaries, organic matter).</t>
-  </si>
-  <si>
-    <t>e.g., 'Greyscale thresholding (Avizo Fire 8.1)' | 'Machine learning (Dragonfly 2022)' | 'Manual tracing' | 'Region growing' | 'None'</t>
-  </si>
-  <si>
-    <t>Image denoising, binarization, and segmentation; 3D model established using Avizo 7 and Multiple-point geostatistics</t>
-  </si>
-  <si>
-    <t>Semi-automatic porosity segmentation by grayscale thresholding; pore volume reconstruction using FEI Avizo Fire 8.1.1; connected component analysis for pore network extraction (PNE)</t>
-  </si>
-  <si>
-    <t>6. Quality Control &amp; Uncertainty</t>
-  </si>
-  <si>
-    <t>Additional Notes</t>
-  </si>
-  <si>
-    <t>Any additional context about this protocol or analysis session not captured by structured fields above.</t>
-  </si>
-  <si>
-    <t>Free text</t>
-  </si>
-  <si>
-    <t>$.schema:description</t>
-  </si>
-  <si>
-    <t>method Property: schema:description accepts free-text narrative; additional notes can extend it or be distributed to the most relevant workflow step's schema:description.</t>
-  </si>
-  <si>
-    <t>method property : description
-  datatype: text
-  readOnly:false</t>
-  </si>
-  <si>
-    <t>Sample imaged without coating; initial ~5% beam-induced shrinkage observed upon first e-beam exposure; sample stable thereafter; focusing performed away from particles of interest to minimise beam exposure</t>
-  </si>
-  <si>
-    <t>EBSD done in variable pressure mode (25 Pa) to suppress charging on tilted sample; spatial resolution ~30 nm stated; calibrated with single-crystal silicon standard</t>
-  </si>
-  <si>
-    <t>CL color imaging also done with separate luminoscope ELM-3R (cold cathode, 10 kV, 0.5 mA, &lt;100 Torr) — standalone CL system, not SEM-based; spectrum deconvolution via Peak Analyzer in OriginPro 8J SR2</t>
-  </si>
-  <si>
-    <t>Described as semiquantitative; BSE images also captured with this instrument at same conditions; EPMA (JEOL JXA-8900R WDS) used for quantitative analyses (out of scope)</t>
-  </si>
-  <si>
-    <t>Digiscan II beam controller used for CL raster; multi-channel color CL distinguishes ~4 spectral bands; beam-induced CL may persist from long-lived IR emission in carbonates</t>
-  </si>
-  <si>
-    <t>Full spectral imaging (Quartz XOne): all X-rays recorded per pixel, allowing post-hoc spectral analysis</t>
-  </si>
-  <si>
-    <t>Additional BSE and EDX analyses also carried out with Hitachi S-4300SE/N (Texas Tech) and Hitachi SU6600 (UWO) — not captured as separate assessment columns</t>
-  </si>
-  <si>
-    <t>Pore and mineral sizes &gt;0.1 µm measured; minerals analyzed via EDS (surface energy spectrum analysis); magnification range 10³ to 10⁴</t>
-  </si>
-  <si>
-    <t>Pore and mineral sizes &gt;20 nm to &lt;5 µm measured; EDS also used for mineral analysis; magnification range 10³ to 10⁵</t>
-  </si>
-  <si>
-    <t>BSE images obtained from both ZEISS 1550VP FE-SEM and JEOL 8200 electron microprobe (EPMA); quantitative EPMA on JEOL 8200 at 12 kV, 5 nA (out of scope for SEM TAPP)</t>
-  </si>
-  <si>
-    <t>EBSD performed at Caltech GPS Analytical Facility; EPMA (JEOL 8200) used for quantitative chemical analysis (out of scope for SEM TAPP)</t>
-  </si>
-  <si>
-    <t>10 BSE images acquired at ×138 magnification and mosaicked (4 consecutive per row) to cover ~9.7 mm area matching SPIM imagery</t>
-  </si>
-  <si>
-    <t>Spot analysis: 20 kV, 30 µm aperture, 30 s live time per spot, maximum process time (Oxford INCA Energy)</t>
-  </si>
-  <si>
-    <t>EDS mapping: 20 kV, 60 µm aperture, 5 ms dwell per pixel, 1024×768 pixels, 2.5 µm pixel size, ~10 h total; element maps co-registered with BSE images</t>
-  </si>
-  <si>
-    <t>SE imaging used for topographic examination; instrument capability: up to ×200,000 magnification, 5 nm resolution; SE acquired before EDS to minimize charging effects</t>
-  </si>
-  <si>
-    <t>Stage tilt 52° between electron and ion columns; SEM range 20V–30kV and FIB range 500V–30kV (system specs); destriping filter xStripes.jar applied; deconvolves y-axis by y/sin(52°) for pixel scale correction</t>
-  </si>
-  <si>
-    <t>SE and BSE imaging; EDS point spectra; Oxford AZtec system; EDS detector: Oxford Instruments Ultim Max SDD 170 mm²</t>
-  </si>
-  <si>
-    <t>Cold FEG; system range 0.5-30 keV; SE and BSE imaging detectors; also equipped with Oxford Instruments Aztec Live/x-stream/Ultimax 170 SDD EDS; specific operating voltage not stated</t>
-  </si>
-  <si>
-    <t>Cold FEG; system range 0.5-30 keV; SE and BSE imaging; EDS mapping; specific operating voltage not stated</t>
-  </si>
-  <si>
-    <t>Compositional heterogeneity assessed through EDS mapping; no specific kV, current, dwell time stated for S-4800 EDS</t>
-  </si>
-  <si>
-    <t>Sections thinned to electron transparency; BSE/SE images acquired before and after sectioning; methods follow refs. 72-75</t>
-  </si>
-  <si>
-    <t>Thicker sections (&lt;100 nm) for TEM; sections up to 600 nm for Fe-L XANES and tomography</t>
-  </si>
-  <si>
-    <t>Multi-step milling: e-beam C deposition then FIB C capping, 30 kV → 16 kV → 5 kV; Pt weld to Cu half grids</t>
-  </si>
-  <si>
-    <t>CL emitting volume at 5 keV: up to 230 nm depth, 200 nm sideways (assuming 100-nm graphite coating); recording below focal plane for magnifications &lt;×500 to minimize hotspot effect</t>
-  </si>
-  <si>
-    <t>SEM-EDS (referred to as SEM-EDX in Extended Data Fig. 8) used to confirm phase identifications of two O-rich presolar grains identified by NanoSIMS isotope mapping: one grain confirmed as ferromagnesian silicate; one confirmed as Al,Mg-bearing oxide (Barnes et al. 2025, p.2 and Extended Data Fig. 8 caption). No instrument name, accelerating voltage, beam current, or sample preparation specifics stated for the JSC SEM-EDS step in this paper.</t>
-  </si>
-  <si>
-    <t>No BSE imaging with FEI Quanta 3D DualBeam or Helios DualBeam at NASA JSC described in this paper (Barnes et al. 2025). BSE mosaic imaging was performed using a Hitachi TM4000plus at the University of Arizona (K-ALFAA) at 15-keV electron beam to identify suitable matrix areas for NanoSIMS analysis (Methods, p.11). No JSC BSE imaging conditions or instrument stated.</t>
-  </si>
-  <si>
-    <t>No FIB-based TEM sample preparation at NASA JSC described in this paper (Barnes et al. 2025). This paper does not include TEM analysis or FIB-SEM-based sample preparation. FIB-based TEM foil preparation using FEI Helios G4 and related instruments at NASA JSC is described in the companion paper Zega et al. 2025 (Nat. Geosci., ref. 7 therein).</t>
-  </si>
-  <si>
-    <t>No FIB-based TEM sample preparation at NASA JSC described in this paper (Barnes et al. 2025). This paper does not include TEM analysis or FIB-SEM-based sample preparation. TEM foil preparation using FEI Helios 660 G3 and related instruments at NASA JSC is described in the companion paper Zega et al. 2025 (Nat. Geosci., ref. 7 therein).</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Mandatory for protocol registration. Must be provided to register a valid protocol.</t>
-  </si>
-  <si>
-    <t>Directly imported from the registered protocol; cannot be changed by the analyst. Changing this value means running a different protocol. Also used for fields relevant only at protocol level — the value is inherited from the protocol record and shown read-only in the analysis form.</t>
-  </si>
-  <si>
-    <t>Optional for protocol registration. Strongly recommended but not required.</t>
-  </si>
-  <si>
-    <t>Imported from the registered protocol but may be adjusted within protocol-defined bounds (e.g., daily tuning, minor software updates). The protocol registers the target or typical value; the analyst confirms or adjusts it. Cannot be left void if the protocol-level tier is Basic.</t>
-  </si>
-  <si>
-    <t>Not applicable at protocol level. This field captures analysis-level information only.</t>
-  </si>
-  <si>
-    <t>Mandatory user input at analysis time. Value comes from the analysis (procedure) itself and cannot be pre-specified in the protocol.</t>
-  </si>
-  <si>
-    <t>Optional user input at analysis time. Recommended for complete and reproducible documentation.</t>
-  </si>
-  <si>
-    <t>Mode Column</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>This field applies to this analytical mode and should be reported.</t>
-  </si>
-  <si>
-    <t>This field does not apply to this analytical mode.</t>
   </si>
   <si>
     <t>property:samplePreparationMethodMethod
@@ -1516,19 +699,417 @@
 readOnly: False</t>
   </si>
   <si>
-    <t>$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation']</t>
+    <t>HCl and HF acid dissolution residue from pristine Tagish Lake pieces; deposited on lacey C TEM grid attached to Al-SEM stub; uncoated</t>
+  </si>
+  <si>
+    <t>Carbon-coated polished thin sections; high vacuum analysis</t>
+  </si>
+  <si>
+    <t>Small coal pillars (~2 mm diameter, 2 mm height) drilled orthogonal to bedding; polished with cross section polisher to remove ~1-2 µm oxide layer; no coating applied</t>
+  </si>
+  <si>
+    <t>Bulk coal polished to ~10 mm × 2-3 mm using polishing and burnishing machine; further polished with cross section polisher; thin gold coating applied by sputtering</t>
+  </si>
+  <si>
+    <t>Polished thin section (section 126A prepared from Grain 126); no coating or SEM-specific preparation stated</t>
+  </si>
+  <si>
+    <t>Polished thin section (section 126A prepared from Grain 126); no coating or EBSD-specific preparation stated</t>
+  </si>
+  <si>
+    <t>Embedded in epoxy, polished to ¼ µm level, sputtered with 30-nm-thick carbon film</t>
+  </si>
+  <si>
+    <t>Cuboidal samples (~0.5×1×1 cm) polished with dry emery paper and argon ion polishing; high-pressure freezing and freeze-drying; glued onto sample holder</t>
+  </si>
+  <si>
+    <t>Attached to Al cylinder SEM mount with double-sided C tape; sputter coated with ~5 nm carbon</t>
+  </si>
+  <si>
+    <t>Polished sections; coated with 0.1 nm carbon for charge mitigation</t>
+  </si>
+  <si>
+    <t>Sections extracted from fine-grained matrix areas in polished sections; BSE and SE images acquired before and after sectioning</t>
+  </si>
+  <si>
+    <t>Particles placed on PELCO carbon conductive tabs on Al SEM round; no protective coating stated</t>
+  </si>
+  <si>
+    <t>Particles dispersed on conductive carbon dots on Al SEM pin mounts</t>
+  </si>
+  <si>
+    <t>Polished thin sections; ~100 nm graphite coating (as stated in CL emitting volume calculation)</t>
+  </si>
+  <si>
+    <t>Sample Name</t>
+  </si>
+  <si>
+    <t>Name or identifier of the sample or sample mount analyzed in this session.</t>
+  </si>
+  <si>
+    <t>e.g., 'Bennu OREX-800045-103' | 'NWA 8657 polished thin section 1'</t>
+  </si>
+  <si>
+    <t>$Dataset.prov:wasGeneratedBy.schema:object[@type ="schema:Thing",            "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:name</t>
+  </si>
+  <si>
+    <t>Section 126A (USNM 7908)</t>
+  </si>
+  <si>
+    <t>NWA 7317</t>
+  </si>
+  <si>
+    <t>SC; HBC</t>
+  </si>
+  <si>
+    <t>OREX-501018-100</t>
+  </si>
+  <si>
+    <t>Sample Persistent Identifier</t>
+  </si>
+  <si>
+    <t>Persistent identifier (e.g., IGSN) for the sample analyzed.</t>
+  </si>
+  <si>
+    <t>URI / IGSN</t>
+  </si>
+  <si>
+    <t>e.g., 'IGSN:AU1234567'</t>
+  </si>
+  <si>
+    <t>$Dataset.prov:wasGeneratedBy.schema:object[@type = "schema:Thing",  "https://w3id.org/isample/vocabulary/materialsampleobjecttype/materialsample"].schema:identifier</t>
+  </si>
+  <si>
+    <t>USNM 7908 (section 126A)</t>
+  </si>
+  <si>
+    <t>3. Instrument &amp; Software</t>
+  </si>
+  <si>
+    <t>Instrument Manufacturer</t>
+  </si>
+  <si>
+    <t>Make of the SEM or FIB-SEM instrument.</t>
+  </si>
+  <si>
+    <t>JEOL | Zeiss | FEI / Thermo Fisher Scientific | Hitachi | Tescan | Phenom | Other: specify | Unknown | N/A | None</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument.schema:manufacturer.schema:Organization.schema:name</t>
+  </si>
+  <si>
+    <t>match. CDIF instrument inherits schema.org Product's schema:manufacturer.</t>
+  </si>
+  <si>
+    <t>FEI</t>
+  </si>
+  <si>
+    <t>Zeiss</t>
+  </si>
+  <si>
+    <t>JEOL</t>
+  </si>
+  <si>
+    <t>Hitachi</t>
+  </si>
+  <si>
+    <t>Other: Leo Electron Microscopy (now Zeiss)</t>
+  </si>
+  <si>
+    <t>Carl Zeiss</t>
+  </si>
+  <si>
+    <t>FEI Company, USA</t>
+  </si>
+  <si>
+    <t>ZEISS (Carl Zeiss)</t>
+  </si>
+  <si>
+    <t>FEI (now Thermo Fisher Scientific)</t>
+  </si>
+  <si>
+    <t>Thermo Fisher Scientific (ThermoScientific)</t>
+  </si>
+  <si>
+    <t>Instrument Model</t>
+  </si>
+  <si>
+    <t>Model designation of the SEM or FIB-SEM instrument, including generation suffix if applicable.</t>
+  </si>
+  <si>
+    <t>e.g., 'JEOL JSM-7600F' | 'Zeiss Supra 55 FEG-SEM' | 'FEI Quanta 650 FEG' | 'Thermo Fisher Quattro S' | 'FEI Helios NanoLab 660' | 'Zeiss Crossbeam 540'</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument.schema:model.schema:name</t>
+  </si>
+  <si>
+    <t>match. CDIF instrument inherits schema.org Product's schema:model.</t>
+  </si>
+  <si>
+    <t>Nova 200 NanoLab DualBeam</t>
+  </si>
+  <si>
+    <t>ZEISS 1550VP</t>
+  </si>
+  <si>
+    <t>JSM-5410LV</t>
+  </si>
+  <si>
+    <t>S-2500C</t>
+  </si>
+  <si>
+    <t>Leo 440</t>
+  </si>
+  <si>
+    <t>Leo 1540 FIB/SEM CrossBeam</t>
+  </si>
+  <si>
+    <t>Crossbeam 540</t>
+  </si>
+  <si>
+    <t>Quanta 250</t>
+  </si>
+  <si>
+    <t>SUPRA 55</t>
+  </si>
+  <si>
+    <t>1550VP</t>
+  </si>
+  <si>
+    <t>Supra 40</t>
+  </si>
+  <si>
+    <t>Helios NanoLab 650</t>
+  </si>
+  <si>
+    <t>7600F</t>
+  </si>
+  <si>
+    <t>S-4800</t>
+  </si>
+  <si>
+    <t>Helios G3</t>
+  </si>
+  <si>
+    <t>Helios G4 UX</t>
+  </si>
+  <si>
+    <t>Quanta 3D 600</t>
+  </si>
+  <si>
+    <t>JSM-7000F</t>
+  </si>
+  <si>
+    <t>Electron Source</t>
+  </si>
+  <si>
+    <t>Type of electron gun used in the SEM instrument.</t>
+  </si>
+  <si>
+    <t>Cold-FEG | Schottky FEG | LaB6 / CeB6 | Tungsten (W) | Other: specify | Unknown | N/A | None</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'ElectronSource'].schema:name</t>
+  </si>
+  <si>
+    <t>match. Electron source/gun modelled as a sub-component of the instrument via schema:hasPart[]; classify the part via schema:additionalType (e.g. 'ElectronGun:FEG') and carry the label in schema:name.</t>
+  </si>
+  <si>
+    <t>Other: FEG (type not specified in paper)</t>
+  </si>
+  <si>
+    <t>Tungsten (W)</t>
+  </si>
+  <si>
+    <t>Other: FEG (type not specified)</t>
+  </si>
+  <si>
+    <t>Field emission gun (FEG)</t>
+  </si>
+  <si>
+    <t>Cold field emission gun (cold FEG)</t>
+  </si>
+  <si>
+    <t>Instrument Variant</t>
+  </si>
+  <si>
+    <t>Broad platform type of the instrument. 'Standard SEM': dedicated electron-only SEM column. 'FIB-SEM dual-beam': combined focused ion beam and SEM columns (enables TEM specimen preparation, 3D serial sectioning, ion-beam milling). 'VP-SEM / ESEM': variable-pressure or environmental SEM for imaging uncoated, hydrated, or charging specimens. An instrument may combine categories (e.g., FIB-SEM with VP capability).</t>
+  </si>
+  <si>
+    <t>Standard SEM | FIB-SEM dual-beam | VP-SEM / ESEM | FIB-SEM dual-beam + VP | Other: specify | N/A | None</t>
   </si>
   <si>
     <t>$MethodDefinition.schema:instrument.schema:additionalType[]</t>
   </si>
   <si>
+    <t xml:space="preserve">enum: {Standard SEM | FIB-SEM dual-beam | VP-SEM / ESEM | FIB-SEM dual-beam + VP | Other: specify | N/A | None} 
+readOnly: True </t>
+  </si>
+  <si>
+    <t>FIB-SEM dual-beam</t>
+  </si>
+  <si>
+    <t>VP-SEM / ESEM</t>
+  </si>
+  <si>
+    <t>Standard SEM</t>
+  </si>
+  <si>
+    <t>ESEM (Environmental SEM)</t>
+  </si>
+  <si>
+    <t>FESEM (Field Emission SEM)</t>
+  </si>
+  <si>
+    <t>VP (Variable Pressure)</t>
+  </si>
+  <si>
+    <t>Dual Beam (FIB-SEM)</t>
+  </si>
+  <si>
+    <t>Ion Beam Source</t>
+  </si>
+  <si>
+    <t>Ion beam source type in a FIB-SEM dual-beam system. Gallium LMIS (Ga+) is the most common ion source; xenon plasma FIB (PFIB) provides higher material removal rates for large-volume milling; helium and neon ion microscopes (GFIS) provide nanometre-resolution imaging and low-damage milling.</t>
+  </si>
+  <si>
+    <t>Gallium LMIS (Ga+) | Xenon plasma FIB (PFIB) | Helium GFIS | Neon GFIS | Other: specify | N/A | None</t>
+  </si>
+  <si>
+    <t>FIB-SEM specific</t>
+  </si>
+  <si>
     <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'IonBeamSource'].schema.name</t>
   </si>
   <si>
+    <t xml:space="preserve">enum: {Gallium LMIS (Ga+) | Xenon plasma FIB (PFIB) | Helium GFIS | Neon GFIS | Other: specify | N/A | None} 
+readOnly: True </t>
+  </si>
+  <si>
+    <t>Gallium LMIS (Ga+)</t>
+  </si>
+  <si>
+    <t>Gallium (Ga+) ion beam</t>
+  </si>
+  <si>
+    <t>SE Detector Type</t>
+  </si>
+  <si>
+    <t>Type of secondary electron detector used. Everhart-Thornley (ET) detector is the standard off-axis collector sensitive to SE2 and some BSE; in-lens (TLD) detectors collect high-resolution SE1 signal at short working distances; GSED/ESED detectors operate in VP/ESEM mode by using the chamber gas as the signal amplification medium.</t>
+  </si>
+  <si>
+    <t>Everhart-Thornley (ET) | In-lens / TLD (through-the-lens) | GSED (VP/ESEM) | ESED (VP/ESEM) | Other: specify | N/A | None</t>
+  </si>
+  <si>
     <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'SE_Detector'].schema.name</t>
   </si>
   <si>
+    <t xml:space="preserve">enum: {Everhart-Thornley (ET) | In-lens / TLD (through-the-lens) | GSED (VP/ESEM) | ESED (VP/ESEM) | Other: specify | N/A | None} 
+readOnly: True </t>
+  </si>
+  <si>
+    <t>In-lens / TLD (through-the-lens)</t>
+  </si>
+  <si>
+    <t>BSE Detector Type</t>
+  </si>
+  <si>
+    <t>Type of backscattered electron detector. Solid-state diode detectors (single or segmented) are standard; YAG scintillator detectors offer high sensitivity at low voltage. Segmented detectors can operate in composition mode (segments summed) or topography mode (differential signal between segments). In-lens BSE detectors provide improved BSE collection at short working distances.</t>
+  </si>
+  <si>
+    <t>Solid-state diode (single) | Solid-state diode (segmented, composition mode) | Solid-state diode (segmented, topography mode) | In-lens BSE | YAG scintillator | Other: specify | N/A | None</t>
+  </si>
+  <si>
     <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'BSE_Detector'].schema.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enum: {Solid-state diode (single) | Solid-state diode (segmented, composition mode) | Solid-state diode (segmented, topography mode) | In-lens BSE | YAG scintillator | Other: specify | N/A | None} 
+readOnly: True </t>
+  </si>
+  <si>
+    <t>Solid-state BSE detector</t>
+  </si>
+  <si>
+    <t>Quadrant Backscatter Detector (QBSD)</t>
+  </si>
+  <si>
+    <t>Acquisition Software</t>
+  </si>
+  <si>
+    <t>Software used to control the SEM and acquire data, including version number. For FIB-SEM 3D tomography, include the automated slice-and-view module name and version.</t>
+  </si>
+  <si>
+    <t>e.g., 'JEOL Analysis Station v3.5' | 'Oxford AZtec 6.0' | 'Zeiss SmartSEM 6.06' | 'Thermo Fisher Auto Slice and View G4 (3D tomography)'</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.bios:computationalTool[]</t>
+  </si>
+  <si>
+    <t>match. bios:computationalTool[] with ada:toolRole='acquisition' captures the acquisition/automation software; schema:name, schema:version, and schema:url are siblings.</t>
+  </si>
+  <si>
+    <t>toolRole = acquisition</t>
+  </si>
+  <si>
+    <t>Gatan DigitalMicrograph (CL image assembly)</t>
+  </si>
+  <si>
+    <t>Oxford INCA Energy</t>
+  </si>
+  <si>
+    <t>Oxford AZtec (Point &amp; ID programme)</t>
+  </si>
+  <si>
+    <t>Oxford Instruments Aztec Live/x-stream</t>
+  </si>
+  <si>
+    <t>Data Reduction Software</t>
+  </si>
+  <si>
+    <t>Software used for post-acquisition data reduction and analysis. List all packages with version numbers.</t>
+  </si>
+  <si>
+    <t>e.g., 'Oxford AZtec 6.0 (EDS quantification); Oxford AZtec Crystal 2.1 (EBSD); Gatan DigitalMicrograph 3.5 (CL); FIJI 2.15 (image processing); Avizo 2023 (3D segmentation)'</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>match. Same container as row 20 with ada:toolRole='reduction' for matrix-correction/data-reduction software.
+validation: null if ada:analyticalMode not '3D Tomography'</t>
+  </si>
+  <si>
+    <t>toolRole = data reduction</t>
+  </si>
+  <si>
+    <t>Gatan DigitalMicrograph</t>
+  </si>
+  <si>
+    <t>Avizo 7 (3D digital core software); Multiple-point geostatistics for pore network model</t>
+  </si>
+  <si>
+    <t>Oxford INCA Energy (semi-quantitative phase determination from atomic proportions)</t>
+  </si>
+  <si>
+    <t>Fiji/ImageJ (StackReg/TurboReg for slice alignment; VolumeJ for volume rendering); Adobe Photoshop CS6 (image enhancement); FEI Avizo Fire 8.1.1 (pore volume reconstruction and segmentation)</t>
+  </si>
+  <si>
+    <t>Oxford AZtec</t>
+  </si>
+  <si>
+    <t>Oxford Instruments Aztec</t>
+  </si>
+  <si>
+    <t>4. Measurement Information</t>
+  </si>
+  <si>
+    <t>Analytical Mode</t>
+  </si>
+  <si>
+    <t>Primary analytical mode(s) executed under this protocol. For multi-mode protocols (e.g., simultaneous BSE + EDS mapping), list all active modes.</t>
+  </si>
+  <si>
+    <t>SE Imaging | BSE Imaging | EDS | SEM-WDS | CL | EBSD | TEM Sample Preparation | 3D Tomography | Multiple (specify) | Other: specify | N/A | None</t>
   </si>
   <si>
     <t>$MethodDefinition.ada:analyticalMode</t>
@@ -1540,6 +1121,122 @@
 enum {SE Imaging | BSE Imaging | EDS | SEM-WDS | CL | EBSD | TEM Sample Preparation | 3D Tomography | Multiple (specify) | Other: specify | N/A | None}</t>
   </si>
   <si>
+    <t>SE Imaging</t>
+  </si>
+  <si>
+    <t>BSE Imaging</t>
+  </si>
+  <si>
+    <t>EDS</t>
+  </si>
+  <si>
+    <t>EBSD</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>BSE (QBSD mode)</t>
+  </si>
+  <si>
+    <t>Spot analysis</t>
+  </si>
+  <si>
+    <t>Element mapping</t>
+  </si>
+  <si>
+    <t>Sequential FIB-SEM tomography (serial cross-section imaging)</t>
+  </si>
+  <si>
+    <t>Low-angle backscattered electron (BSE) imaging</t>
+  </si>
+  <si>
+    <t>Point spectra (spot analysis, Point &amp; ID)</t>
+  </si>
+  <si>
+    <t>EDS mapping</t>
+  </si>
+  <si>
+    <t>In-situ FIB lift-out; cross-section lamella preparation for TEM</t>
+  </si>
+  <si>
+    <t>In-situ FIB lift-out; lamella preparation for XANES and TEM</t>
+  </si>
+  <si>
+    <t>In-situ FIB lift-out; cross-section lamella preparation</t>
+  </si>
+  <si>
+    <t>Panchromatic CL imaging; hyperspectral CL; monochromatic CL imaging</t>
+  </si>
+  <si>
+    <t>Elemental maps and spot spectra (SEM-EDX) for presolar grain phase identification</t>
+  </si>
+  <si>
+    <t>Accelerating Voltage</t>
+  </si>
+  <si>
+    <t>Electron beam accelerating voltage in kilovolts. Affects X-ray generation depth (EDS/WDS), EBSD pattern quality, imaging resolution, and beam penetration. Low voltages (1-5 kV) improve surface sensitivity and reduce beam damage; high voltages (15-20 kV) improve X-ray generation for quantitative analysis.</t>
+  </si>
+  <si>
+    <t>Numeric (kV)</t>
+  </si>
+  <si>
+    <t>e.g., 2 | 5 | 10 | 15 | 20</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.ada:acceleratingVoltage</t>
+  </si>
+  <si>
+    <t>property: acceleratingVoltage
+read-only: false
+datatype: string</t>
+  </si>
+  <si>
+    <t>500 V; 1 kV; 5 kV</t>
+  </si>
+  <si>
+    <t>10 kV</t>
+  </si>
+  <si>
+    <t>20 kV</t>
+  </si>
+  <si>
+    <t>15 kV</t>
+  </si>
+  <si>
+    <t>15–20 kV</t>
+  </si>
+  <si>
+    <t>2 kV (SEM imaging)</t>
+  </si>
+  <si>
+    <t>30 keV (FIB milling and thinning)</t>
+  </si>
+  <si>
+    <t>16 to 30 keV (coarse milling); down to 1 keV (polishing)</t>
+  </si>
+  <si>
+    <t>30 kV (initial milling); 16 kV (intermediate); 5 kV (final thinning)</t>
+  </si>
+  <si>
+    <t>5 keV</t>
+  </si>
+  <si>
+    <t>Beam Current</t>
+  </si>
+  <si>
+    <t>Electron beam probe current. Higher current improves signal-to-noise for X-ray analysis (EDS/WDS, EBSD) and CL but may increase beam damage and reduce spatial resolution. Express in nA; for sub-nA values use decimal notation (e.g., 0.4 nA).</t>
+  </si>
+  <si>
+    <t>Numeric (nA)</t>
+  </si>
+  <si>
+    <t>e.g., 0.4 | 0.9 | 2 | 5 | 10 | 20</t>
+  </si>
+  <si>
+    <t>Analyte-Specific for SEM-WDS</t>
+  </si>
+  <si>
     <t>$MethodDefinition.ada:beamCurrent</t>
   </si>
   <si>
@@ -1548,9 +1245,34 @@
 datatype: string</t>
   </si>
   <si>
-    <t>property: acceleratingVoltage
-read-only: false
-datatype: string</t>
+    <t>70 fA (500 V); 1.4 pA (1 kV); 98 pA (5 kV)</t>
+  </si>
+  <si>
+    <t>6 nA</t>
+  </si>
+  <si>
+    <t>2.0 nA</t>
+  </si>
+  <si>
+    <t>~900 pA</t>
+  </si>
+  <si>
+    <t>0.8 to 2.5 nA (thinning)</t>
+  </si>
+  <si>
+    <t>1 to 4 nA</t>
+  </si>
+  <si>
+    <t>Working Distance</t>
+  </si>
+  <si>
+    <t>Distance between the objective lens pole piece and the specimen surface in millimetres. Affects spatial resolution, depth of focus, EDS X-ray take-off angle, and EBSD geometry.</t>
+  </si>
+  <si>
+    <t>Numeric (mm)</t>
+  </si>
+  <si>
+    <t>e.g., 4 | 8 | 10 | 15</t>
   </si>
   <si>
     <t>$MethodDefinition.ada:workingDistance</t>
@@ -1561,10 +1283,37 @@
 datatype: string</t>
   </si>
   <si>
-    <t>$MethodDefinition.ada:acceleratingVoltage</t>
+    <t>0.5–5.4 mm</t>
+  </si>
+  <si>
+    <t>5.4 mm (eucentric height for electron and ion columns)</t>
+  </si>
+  <si>
+    <t>~10 mm</t>
+  </si>
+  <si>
+    <t>8 mm</t>
+  </si>
+  <si>
+    <t>4 mm</t>
+  </si>
+  <si>
+    <t>Dwell Time per Pixel</t>
+  </si>
+  <si>
+    <t>Time the electron beam dwells on each pixel during raster scanning (imaging modes) or on each step position during compositional mapping (EDS and WDS mapping modes), in microseconds or milliseconds. Longer dwell time improves signal-to-noise and counting statistics but increases total dose and can cause beam damage or contamination on sensitive materials. For WDS mapping, the dwell time is per spectrometer per pixel.</t>
+  </si>
+  <si>
+    <t>Numeric + unit</t>
+  </si>
+  <si>
+    <t>e.g., '400 ns' | '10 µs' | '1 ms'</t>
   </si>
   <si>
     <t>$MethodDefinition.ada:dwellTimePerPixel</t>
+  </si>
+  <si>
+    <t>validation: null if ada:analyticalMode not '3D Tomography'</t>
   </si>
   <si>
     <t>property: dwellTimePerPixel
@@ -1572,6 +1321,15 @@
 datatype: string</t>
   </si>
   <si>
+    <t>Protective Coating Deposition</t>
+  </si>
+  <si>
+    <t>Type and deposition conditions of the protective coating applied to the sample surface before FIB milling. E-beam deposition causes less surface damage than ion-beam deposition and should be applied as the initial layer. Typical coatings: platinum (Pt) or carbon (C). State material, deposition method, beam conditions, and approximate thickness.</t>
+  </si>
+  <si>
+    <t>e.g., 'E-beam Pt (5 kV, 1.5 nA, ~500 nm) then Ga+ ion-beam Pt (30 kV, 0.3 nA, ~2 µm)' | 'E-beam C (5 kV) + ion-beam C (2-3 µm total)'</t>
+  </si>
+  <si>
     <t xml:space="preserve">$MethodDefinition.schema:actionProcess.schema:step[][schema:name='samplePreparation'].schema:additionalProperty.schema:name </t>
   </si>
   <si>
@@ -1580,16 +1338,76 @@
 datatype: string</t>
   </si>
   <si>
+    <t>No coating applied; not sputtered with gold or other materials</t>
+  </si>
+  <si>
+    <t>12-µm wide × 4-µm tall carbon capping layer deposited on matrix areas</t>
+  </si>
+  <si>
+    <t>Electron-beam deposited carbon (~0.5–1 µm); followed by ion beam-deposited carbon (~2–3 µm capping layer)</t>
+  </si>
+  <si>
+    <t>Coarse Milling Conditions</t>
+  </si>
+  <si>
+    <t>Ion beam voltage and current used for bulk material removal during FIB milling. For TEM specimen preparation: bulk trenching to isolate the lamella and intermediate thinning. For 3D tomography: face preparation and initial slice removal.</t>
+  </si>
+  <si>
+    <t>e.g., '30 kV, 2.5 nA (bulk trenching); 16 kV, 0.8 nA (intermediate thinning)'</t>
+  </si>
+  <si>
     <t>property: coarseMillingConditions
 read-only: false
 datatype: string</t>
   </si>
   <si>
+    <t>30 kV, 10 pA Ga beam</t>
+  </si>
+  <si>
+    <t>Standard stair step; 30 keV, currents 2.5 to 0.8 nA</t>
+  </si>
+  <si>
+    <t>Ga+ ion beam at 16–30 keV (coarse milling)</t>
+  </si>
+  <si>
+    <t>Ga+ ion beam at 30 kV (initial milling); 16 kV (intermediate)</t>
+  </si>
+  <si>
+    <t>Fine Polishing Conditions</t>
+  </si>
+  <si>
+    <t>Ion beam voltage and current for final thinning and surface polishing of the TEM lamella. Low-voltage polishing (2 kV or below) minimises Ga implantation depth, surface amorphisation, and curtaining artifacts.</t>
+  </si>
+  <si>
+    <t>e.g., '5 kV, 0.3 nA; final polish: 2 kV, 72 pA' | '1 kV, 0.1 nA final step'</t>
+  </si>
+  <si>
+    <t>FIB-SEM specific; TEM Sample Preparation specific</t>
+  </si>
+  <si>
+    <t>validation: null if ada:analyticalMode not 'TEM Sample Preparation'</t>
+  </si>
+  <si>
     <t>property: finePolishingConditions
 read-only: false
 datatype: string</t>
   </si>
   <si>
+    <t>Various voltages down to 1 keV (polishing)</t>
+  </si>
+  <si>
+    <t>Ga+ ion beam at 5 kV (final thinning) until ~100 nm thick</t>
+  </si>
+  <si>
+    <t>Target Foil Thickness</t>
+  </si>
+  <si>
+    <t>Target thickness of the electron-transparent TEM lamella after final FIB polishing, in nanometres. Actual thickness may differ from target. Typical range: 50-150 nm for standard TEM/STEM; 200-600 nm for XANES or tomography sections.</t>
+  </si>
+  <si>
+    <t>e.g., '~100 nm' | '50-80 nm' | '100-200 nm'</t>
+  </si>
+  <si>
     <t>$MethodDefinition.ada:targetFoilThickness</t>
   </si>
   <si>
@@ -1598,15 +1416,42 @@
 datatype: string</t>
   </si>
   <si>
+    <t>&lt;100 to 600 nm (variable, depending on targeted experiment)</t>
+  </si>
+  <si>
+    <t>~100 nm</t>
+  </si>
+  <si>
+    <t>Lift-out Method</t>
+  </si>
+  <si>
+    <t>Method used to transfer the FIB-prepared lamella to the TEM support grid. In-situ lift-out uses a micromanipulator inside the FIB-SEM chamber and is the standard method for small or precious specimens.</t>
+  </si>
+  <si>
+    <t>In-situ (micromanipulator, Cu or Mo TEM half-grid) | Ex-situ | Other: specify | N/A | None</t>
+  </si>
+  <si>
     <t>property: liftOutMethod
 read-only: True
 datatype: number</t>
   </si>
   <si>
-    <t>validation: null if ada:analyticalMode not 'TEM Sample Preparation'</t>
-  </si>
-  <si>
-    <t>validation: null if ada:analyticalMode not '3D Tomography'</t>
+    <t>In-situ lift-out (standard stair step)</t>
+  </si>
+  <si>
+    <t>In-situ lift-out; ion beam-deposited Pt weld to Cu half grids</t>
+  </si>
+  <si>
+    <t>Ion Milling Conditions (3D Tomography)</t>
+  </si>
+  <si>
+    <t>Ion beam voltage and current used to mill each slice during FIB-SEM serial sectioning. These parameters determine material removal rate per slice and exposed surface quality.</t>
+  </si>
+  <si>
+    <t>e.g., 'Ga+ 30 kV, 2.5 nA (slice milling)'</t>
+  </si>
+  <si>
+    <t>FIB-SEM specific; 3D Tomography specific</t>
   </si>
   <si>
     <t>property: ionMillingConditions
@@ -1614,76 +1459,40 @@
 datatype: number</t>
   </si>
   <si>
+    <t>Slice Thickness</t>
+  </si>
+  <si>
+    <t>Thickness of each FIB-milled slice during serial sectioning in nanometres. Controls the Z-axis resolution of the 3D reconstruction.</t>
+  </si>
+  <si>
+    <t>Numeric (nm)</t>
+  </si>
+  <si>
+    <t>e.g., 10 | 20 | 50 | 100</t>
+  </si>
+  <si>
     <t>property: sliceThickness
 read-only: false
 datatype: number</t>
   </si>
   <si>
-    <t>$MethodDefinition.bios:computationalTool[].schema:name='3D image registration'  schema:description</t>
-  </si>
-  <si>
-    <t>$MethodDefinition.bios:computationalTool[].schema:name='3D segmentation method'  schema:description</t>
-  </si>
-  <si>
-    <t>match.   ada:toolRole='processing' ;
-validation: null if ada:analyticalMode not '3D Tomography'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolRole = 'processing'
-read-only: False
-</t>
-  </si>
-  <si>
-    <t>match. Same container as row 20 with ada:toolRole='reduction' for matrix-correction/data-reduction software.
-validation: null if ada:analyticalMode not '3D Tomography'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">readOnly: True </t>
-  </si>
-  <si>
-    <t xml:space="preserve">put text in MonetaryGrant name unless can clearly parse identifier distinct from name. 
-readOnly: True </t>
-  </si>
-  <si>
-    <t xml:space="preserve">target URL to publication , target name should be title of publication 
-readOnly: True </t>
-  </si>
-  <si>
-    <t xml:space="preserve">schema:DefinedTerm.schema:termCode
-datatype: enum {Silicate glass | Feldspar | Pyroxene | Olivine | Oxide | Sulfide | Carbonate | Phosphate | Native metal | Iron meteorite | Fluid inclusion | Melt inclusion | Whole rock | Other: specify} 
-readOnly: True </t>
-  </si>
-  <si>
-    <t xml:space="preserve">enum: {Standard SEM | FIB-SEM dual-beam | VP-SEM / ESEM | FIB-SEM dual-beam + VP | Other: specify | N/A | None} 
-readOnly: True </t>
-  </si>
-  <si>
-    <t xml:space="preserve">enum: {Gallium LMIS (Ga+) | Xenon plasma FIB (PFIB) | Helium GFIS | Neon GFIS | Other: specify | N/A | None} 
-readOnly: True </t>
-  </si>
-  <si>
-    <t xml:space="preserve">enum: {Everhart-Thornley (ET) | In-lens / TLD (through-the-lens) | GSED (VP/ESEM) | ESED (VP/ESEM) | Other: specify | N/A | None} 
-readOnly: True </t>
-  </si>
-  <si>
-    <t xml:space="preserve">enum: {Solid-state diode (single) | Solid-state diode (segmented, composition mode) | Solid-state diode (segmented, topography mode) | In-lens BSE | YAG scintillator | Other: specify | N/A | None} 
-readOnly: True </t>
-  </si>
-  <si>
-    <t>$MethodDefinition.schema:instrument.schema:hasPart[].additionalType[ 'ElectronSource'].schema:name</t>
-  </si>
-  <si>
-    <t>This should be the identifier for the protocol definition that the analysis level 'detail' is extenting for a particular dataset.</t>
-  </si>
-  <si>
-    <t>$Dataset.schema:measuremntTechnique.schema:DefinedTerm.schema.name and schema.identifier</t>
-  </si>
-  <si>
-    <t>Parse into two fields if possible.  validation: null if ada:analyticalMode not '3D Tomography'</t>
+    <t>15 nm (single layer scanning thickness = 9.0 µm total / 600 slices)</t>
+  </si>
+  <si>
+    <t>Voxel Size and Image Stack Dimensions</t>
+  </si>
+  <si>
+    <t>X, Y, Z dimensions of the reconstructed 3D voxel in nanometres (X-Y pixel size from SEM image calibration; Z from slice thickness), and the total number of slices in the stack. Determined at analysis time.</t>
+  </si>
+  <si>
+    <t>e.g., '14.6 x 8.3 x 10.0 nm, 600 slices' | '14.8 x 14.8 x 20 nm, 800 slices'</t>
   </si>
   <si>
     <t>$Dataset.ada:voxelSize   
 $Dataset.ada:sliceCount</t>
+  </si>
+  <si>
+    <t>Parse into two fields if possible.  validation: null if ada:analyticalMode not '3D Tomography'</t>
   </si>
   <si>
     <t>property- ada:voxelSize
@@ -1694,10 +1503,198 @@
 required</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>optional</t>
+    <t>9.8 × 9.8 × 15 nm voxel size; 600 slices; 7.8 × 7.8 µm scanning area; 9.0 µm total thickness</t>
+  </si>
+  <si>
+    <t>14.8×14.8 nm pixel size (XY); ~800 total slices; sub-volumes: SC=5.609×3.08×5.446 µm; HBC=4.679×3.2×4.24 µm; SEM image resolution 2.5 nm</t>
+  </si>
+  <si>
+    <t>5. Data Processing</t>
+  </si>
+  <si>
+    <t>3D Image Registration</t>
+  </si>
+  <si>
+    <t>Method used to align consecutive SEM image slices in the 3D stack to correct for drift, vibration, and curtaining artifacts. Include software used.</t>
+  </si>
+  <si>
+    <t>e.g., 'Cross-correlation (FIJI/ImageJ)' | 'Fiducial marker alignment' | 'Auto Slice and View G3 built-in drift correction' | 'Avizo drift correction'</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.bios:computationalTool[].schema:name='3D image registration'  schema:description</t>
+  </si>
+  <si>
+    <t>match.   ada:toolRole='processing' ;
+validation: null if ada:analyticalMode not '3D Tomography'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolRole = 'processing'
+read-only: False
+</t>
+  </si>
+  <si>
+    <t>Fiji/ImageJ StackReg and TurboReg plugins used for slice realignment</t>
+  </si>
+  <si>
+    <t>3D Segmentation Method</t>
+  </si>
+  <si>
+    <t>Method and software used to segment phases and features in the aligned 3D image stack, transforming the grayscale stack into labelled 3D regions (pores, mineral phases, grain boundaries, organic matter).</t>
+  </si>
+  <si>
+    <t>e.g., 'Greyscale thresholding (Avizo Fire 8.1)' | 'Machine learning (Dragonfly 2022)' | 'Manual tracing' | 'Region growing' | 'None'</t>
+  </si>
+  <si>
+    <t>$MethodDefinition.bios:computationalTool[].schema:name='3D segmentation method'  schema:description</t>
+  </si>
+  <si>
+    <t>Image denoising, binarization, and segmentation; 3D model established using Avizo 7 and Multiple-point geostatistics</t>
+  </si>
+  <si>
+    <t>Semi-automatic porosity segmentation by grayscale thresholding; pore volume reconstruction using FEI Avizo Fire 8.1.1; connected component analysis for pore network extraction (PNE)</t>
+  </si>
+  <si>
+    <t>6. Quality Control &amp; Uncertainty</t>
+  </si>
+  <si>
+    <t>Additional Notes</t>
+  </si>
+  <si>
+    <t>Any additional context about this protocol or analysis session not captured by structured fields above.</t>
+  </si>
+  <si>
+    <t>Free text</t>
+  </si>
+  <si>
+    <t>$.schema:description</t>
+  </si>
+  <si>
+    <t>method Property: schema:description accepts free-text narrative; additional notes can extend it or be distributed to the most relevant workflow step's schema:description.</t>
+  </si>
+  <si>
+    <t>method property : description
+  datatype: text
+  readOnly:false</t>
+  </si>
+  <si>
+    <t>Sample imaged without coating; initial ~5% beam-induced shrinkage observed upon first e-beam exposure; sample stable thereafter; focusing performed away from particles of interest to minimise beam exposure</t>
+  </si>
+  <si>
+    <t>EBSD done in variable pressure mode (25 Pa) to suppress charging on tilted sample; spatial resolution ~30 nm stated; calibrated with single-crystal silicon standard</t>
+  </si>
+  <si>
+    <t>CL color imaging also done with separate luminoscope ELM-3R (cold cathode, 10 kV, 0.5 mA, &lt;100 Torr) — standalone CL system, not SEM-based; spectrum deconvolution via Peak Analyzer in OriginPro 8J SR2</t>
+  </si>
+  <si>
+    <t>Described as semiquantitative; BSE images also captured with this instrument at same conditions; EPMA (JEOL JXA-8900R WDS) used for quantitative analyses (out of scope)</t>
+  </si>
+  <si>
+    <t>Digiscan II beam controller used for CL raster; multi-channel color CL distinguishes ~4 spectral bands; beam-induced CL may persist from long-lived IR emission in carbonates</t>
+  </si>
+  <si>
+    <t>Full spectral imaging (Quartz XOne): all X-rays recorded per pixel, allowing post-hoc spectral analysis</t>
+  </si>
+  <si>
+    <t>Additional BSE and EDX analyses also carried out with Hitachi S-4300SE/N (Texas Tech) and Hitachi SU6600 (UWO) — not captured as separate assessment columns</t>
+  </si>
+  <si>
+    <t>Pore and mineral sizes &gt;0.1 µm measured; minerals analyzed via EDS (surface energy spectrum analysis); magnification range 10³ to 10⁴</t>
+  </si>
+  <si>
+    <t>Pore and mineral sizes &gt;20 nm to &lt;5 µm measured; EDS also used for mineral analysis; magnification range 10³ to 10⁵</t>
+  </si>
+  <si>
+    <t>BSE images obtained from both ZEISS 1550VP FE-SEM and JEOL 8200 electron microprobe (EPMA); quantitative EPMA on JEOL 8200 at 12 kV, 5 nA (out of scope for SEM TAPP)</t>
+  </si>
+  <si>
+    <t>EBSD performed at Caltech GPS Analytical Facility; EPMA (JEOL 8200) used for quantitative chemical analysis (out of scope for SEM TAPP)</t>
+  </si>
+  <si>
+    <t>10 BSE images acquired at ×138 magnification and mosaicked (4 consecutive per row) to cover ~9.7 mm area matching SPIM imagery</t>
+  </si>
+  <si>
+    <t>Spot analysis: 20 kV, 30 µm aperture, 30 s live time per spot, maximum process time (Oxford INCA Energy)</t>
+  </si>
+  <si>
+    <t>EDS mapping: 20 kV, 60 µm aperture, 5 ms dwell per pixel, 1024×768 pixels, 2.5 µm pixel size, ~10 h total; element maps co-registered with BSE images</t>
+  </si>
+  <si>
+    <t>SE imaging used for topographic examination; instrument capability: up to ×200,000 magnification, 5 nm resolution; SE acquired before EDS to minimize charging effects</t>
+  </si>
+  <si>
+    <t>Stage tilt 52° between electron and ion columns; SEM range 20V–30kV and FIB range 500V–30kV (system specs); destriping filter xStripes.jar applied; deconvolves y-axis by y/sin(52°) for pixel scale correction</t>
+  </si>
+  <si>
+    <t>SE and BSE imaging; EDS point spectra; Oxford AZtec system; EDS detector: Oxford Instruments Ultim Max SDD 170 mm²</t>
+  </si>
+  <si>
+    <t>Cold FEG; system range 0.5-30 keV; SE and BSE imaging detectors; also equipped with Oxford Instruments Aztec Live/x-stream/Ultimax 170 SDD EDS; specific operating voltage not stated</t>
+  </si>
+  <si>
+    <t>Cold FEG; system range 0.5-30 keV; SE and BSE imaging; EDS mapping; specific operating voltage not stated</t>
+  </si>
+  <si>
+    <t>Compositional heterogeneity assessed through EDS mapping; no specific kV, current, dwell time stated for S-4800 EDS</t>
+  </si>
+  <si>
+    <t>Sections thinned to electron transparency; BSE/SE images acquired before and after sectioning; methods follow refs. 72-75</t>
+  </si>
+  <si>
+    <t>Thicker sections (&lt;100 nm) for TEM; sections up to 600 nm for Fe-L XANES and tomography</t>
+  </si>
+  <si>
+    <t>Multi-step milling: e-beam C deposition then FIB C capping, 30 kV → 16 kV → 5 kV; Pt weld to Cu half grids</t>
+  </si>
+  <si>
+    <t>CL emitting volume at 5 keV: up to 230 nm depth, 200 nm sideways (assuming 100-nm graphite coating); recording below focal plane for magnifications &lt;×500 to minimize hotspot effect</t>
+  </si>
+  <si>
+    <t>SEM-EDS (referred to as SEM-EDX in Extended Data Fig. 8) used to confirm phase identifications of two O-rich presolar grains identified by NanoSIMS isotope mapping: one grain confirmed as ferromagnesian silicate; one confirmed as Al,Mg-bearing oxide (Barnes et al. 2025, p.2 and Extended Data Fig. 8 caption). No instrument name, accelerating voltage, beam current, or sample preparation specifics stated for the JSC SEM-EDS step in this paper.</t>
+  </si>
+  <si>
+    <t>No BSE imaging with FEI Quanta 3D DualBeam or Helios DualBeam at NASA JSC described in this paper (Barnes et al. 2025). BSE mosaic imaging was performed using a Hitachi TM4000plus at the University of Arizona (K-ALFAA) at 15-keV electron beam to identify suitable matrix areas for NanoSIMS analysis (Methods, p.11). No JSC BSE imaging conditions or instrument stated.</t>
+  </si>
+  <si>
+    <t>No FIB-based TEM sample preparation at NASA JSC described in this paper (Barnes et al. 2025). This paper does not include TEM analysis or FIB-SEM-based sample preparation. FIB-based TEM foil preparation using FEI Helios G4 and related instruments at NASA JSC is described in the companion paper Zega et al. 2025 (Nat. Geosci., ref. 7 therein).</t>
+  </si>
+  <si>
+    <t>No FIB-based TEM sample preparation at NASA JSC described in this paper (Barnes et al. 2025). This paper does not include TEM analysis or FIB-SEM-based sample preparation. TEM foil preparation using FEI Helios 660 G3 and related instruments at NASA JSC is described in the companion paper Zega et al. 2025 (Nat. Geosci., ref. 7 therein).</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Mandatory for protocol registration. Must be provided to register a valid protocol.</t>
+  </si>
+  <si>
+    <t>Directly imported from the registered protocol; cannot be changed by the analyst. Changing this value means running a different protocol. Also used for fields relevant only at protocol level — the value is inherited from the protocol record and shown read-only in the analysis form.</t>
+  </si>
+  <si>
+    <t>Optional for protocol registration. Strongly recommended but not required.</t>
+  </si>
+  <si>
+    <t>Imported from the registered protocol but may be adjusted within protocol-defined bounds (e.g., daily tuning, minor software updates). The protocol registers the target or typical value; the analyst confirms or adjusts it. Cannot be left void if the protocol-level tier is Basic.</t>
+  </si>
+  <si>
+    <t>Not applicable at protocol level. This field captures analysis-level information only.</t>
+  </si>
+  <si>
+    <t>Mandatory user input at analysis time. Value comes from the analysis (procedure) itself and cannot be pre-specified in the protocol.</t>
+  </si>
+  <si>
+    <t>Optional user input at analysis time. Recommended for complete and reproducible documentation.</t>
+  </si>
+  <si>
+    <t>Mode Column</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>This field applies to this analytical mode and should be reported.</t>
+  </si>
+  <si>
+    <t>This field does not apply to this analytical mode.</t>
   </si>
 </sst>
 </file>
@@ -1811,7 +1808,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1871,9 +1868,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2178,27 +2172,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AW53"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.921875" customWidth="1"/>
-    <col min="2" max="2" width="23.61328125" customWidth="1"/>
-    <col min="3" max="3" width="8.3828125" customWidth="1"/>
-    <col min="4" max="4" width="7.921875" customWidth="1"/>
-    <col min="5" max="5" width="7.69140625" customWidth="1"/>
-    <col min="6" max="6" width="23.69140625" customWidth="1"/>
-    <col min="7" max="7" width="7.84375" customWidth="1"/>
-    <col min="8" max="8" width="10.3046875" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="7.765625" customWidth="1"/>
-    <col min="10" max="10" width="7.15234375" customWidth="1"/>
-    <col min="11" max="12" width="27.765625" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
-    <col min="14" max="14" width="10.921875" customWidth="1"/>
-    <col min="15" max="46" width="30" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="68" customWidth="1"/>
+    <col min="3" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="22" style="1" customWidth="1"/>
+    <col min="12" max="13" width="30" style="1" customWidth="1"/>
+    <col min="14" max="46" width="30" customWidth="1"/>
+    <col min="47" max="47" width="29.42578125" customWidth="1"/>
+    <col min="48" max="48" width="28.28515625" customWidth="1"/>
+    <col min="49" max="49" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="48.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:49" ht="51" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2347,7 +2340,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>49</v>
       </c>
@@ -2358,49 +2351,122 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
-      <c r="AS2" s="5"/>
-      <c r="AT2" s="5"/>
-      <c r="AU2" s="5"/>
-      <c r="AV2" s="5"/>
-      <c r="AW2" s="5"/>
+      <c r="I2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="W2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW2" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="3" spans="1:49" ht="60.9" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:49" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
@@ -2436,7 +2502,7 @@
         <v>60</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>50</v>
@@ -2547,12 +2613,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="79.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>53</v>
@@ -2561,10 +2627,10 @@
         <v>54</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
@@ -2577,13 +2643,13 @@
         <v>58</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="N4" s="9" t="s">
         <v>50</v>
@@ -2682,7 +2748,7 @@
         <v>50</v>
       </c>
       <c r="AT4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AU4" s="1" t="s">
         <v>50</v>
@@ -2694,12 +2760,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:49" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:49" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>53</v>
@@ -2711,7 +2777,7 @@
         <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
@@ -2724,13 +2790,13 @@
         <v>58</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>50</v>
@@ -2841,24 +2907,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:49" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:49" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
@@ -2871,29 +2937,28 @@
         <v>58</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M6" s="1"/>
+        <v>79</v>
+      </c>
       <c r="N6" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>50</v>
@@ -2902,79 +2967,79 @@
         <v>50</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH6" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AM6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AR6" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AN6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AO6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AP6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AQ6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AR6" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="AS6" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AT6" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AU6" s="1" t="s">
         <v>50</v>
@@ -2986,24 +3051,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:49" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
@@ -3016,12 +3081,11 @@
         <v>58</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="M7" s="1"/>
+        <v>100</v>
+      </c>
       <c r="N7" s="9" t="s">
         <v>50</v>
       </c>
@@ -3131,12 +3195,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:49" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>53</v>
@@ -3145,10 +3209,10 @@
         <v>54</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
@@ -3161,13 +3225,13 @@
         <v>58</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="N8" s="9" t="s">
         <v>50</v>
@@ -3278,15 +3342,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:49" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:49" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>54</v>
@@ -3295,7 +3359,7 @@
         <v>55</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
@@ -3308,13 +3372,13 @@
         <v>58</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>527</v>
+        <v>112</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>50</v>
@@ -3425,24 +3489,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="58.3" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
@@ -3455,13 +3519,13 @@
         <v>58</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>528</v>
+        <v>118</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>50</v>
@@ -3572,24 +3636,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:49" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>53</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1" t="s">
@@ -3602,13 +3666,13 @@
         <v>58</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>536</v>
+        <v>123</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>535</v>
+        <v>124</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>540</v>
+        <v>125</v>
       </c>
       <c r="N11" s="9" t="s">
         <v>50</v>
@@ -3719,15 +3783,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:49" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>53</v>
@@ -3736,7 +3800,7 @@
         <v>55</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
@@ -3749,11 +3813,10 @@
         <v>58</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L12" s="1"/>
+        <v>129</v>
+      </c>
       <c r="M12" s="1" t="s">
-        <v>541</v>
+        <v>130</v>
       </c>
       <c r="N12" s="9" t="s">
         <v>50</v>
@@ -3864,24 +3927,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:49" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
@@ -3894,11 +3957,10 @@
         <v>58</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="L13" s="1"/>
+        <v>133</v>
+      </c>
       <c r="M13" s="1" t="s">
-        <v>541</v>
+        <v>130</v>
       </c>
       <c r="N13" s="9" t="s">
         <v>50</v>
@@ -4009,24 +4071,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:49" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>53</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
@@ -4039,11 +4101,10 @@
         <v>58</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="L14" s="1"/>
+        <v>136</v>
+      </c>
       <c r="M14" s="1" t="s">
-        <v>541</v>
+        <v>130</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>50</v>
@@ -4154,15 +4215,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:49" ht="58.3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:49" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>53</v>
@@ -4171,7 +4232,7 @@
         <v>55</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1" t="s">
@@ -4184,20 +4245,19 @@
         <v>58</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="L15" s="1"/>
+        <v>140</v>
+      </c>
       <c r="M15" s="1" t="s">
-        <v>541</v>
+        <v>130</v>
       </c>
       <c r="N15" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="Q15" s="1" t="s">
         <v>50</v>
@@ -4239,10 +4299,10 @@
         <v>50</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="AF15" s="1" t="s">
         <v>50</v>
@@ -4260,28 +4320,28 @@
         <v>50</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="AL15" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="AO15" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="AP15" s="1" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="AQ15" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="AR15" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="AS15" s="1" t="s">
         <v>50</v>
@@ -4299,24 +4359,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="189.45" hidden="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:49" ht="105" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1" t="s">
@@ -4329,112 +4389,112 @@
         <v>58</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="N16" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AH16" s="1" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AI16" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AJ16" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AK16" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AL16" s="1" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AO16" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="AP16" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AQ16" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="AR16" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AS16" s="1" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AT16" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AU16" s="1" t="s">
         <v>50</v>
@@ -4446,24 +4506,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:49" ht="174.9" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:49" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1" t="s">
@@ -4476,13 +4536,13 @@
         <v>58</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="L17" s="1">
         <v>386</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="N17" s="9" t="s">
         <v>50</v>
@@ -4593,24 +4653,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:49" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1" t="s">
@@ -4623,10 +4683,8 @@
         <v>58</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
+        <v>189</v>
+      </c>
       <c r="N18" s="9" t="s">
         <v>50</v>
       </c>
@@ -4736,24 +4794,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:49" ht="102" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:49" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1" t="s">
@@ -4766,10 +4824,8 @@
         <v>58</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
+        <v>193</v>
+      </c>
       <c r="N19" s="9" t="s">
         <v>50</v>
       </c>
@@ -4879,9 +4935,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:49" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -4890,54 +4946,127 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5"/>
-      <c r="Z20" s="5"/>
-      <c r="AA20" s="5"/>
-      <c r="AB20" s="5"/>
-      <c r="AC20" s="5"/>
-      <c r="AD20" s="5"/>
-      <c r="AE20" s="5"/>
-      <c r="AF20" s="5"/>
-      <c r="AG20" s="5"/>
-      <c r="AH20" s="5"/>
-      <c r="AI20" s="5"/>
-      <c r="AJ20" s="5"/>
-      <c r="AK20" s="5"/>
-      <c r="AL20" s="5"/>
-      <c r="AM20" s="5"/>
-      <c r="AN20" s="5"/>
-      <c r="AO20" s="5"/>
-      <c r="AP20" s="5"/>
-      <c r="AQ20" s="5"/>
-      <c r="AR20" s="5"/>
-      <c r="AS20" s="5"/>
-      <c r="AT20" s="5"/>
-      <c r="AU20" s="5"/>
-      <c r="AV20" s="5"/>
-      <c r="AW20" s="5"/>
+      <c r="I20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="W20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="X20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW20" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="21" spans="1:49" ht="94.3" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:49" ht="150" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>53</v>
@@ -4946,10 +5075,10 @@
         <v>54</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
@@ -4962,112 +5091,112 @@
         <v>58</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>529</v>
+        <v>201</v>
       </c>
       <c r="N21" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="AH21" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="AI21" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AL21" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="AN21" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="AO21" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="AP21" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="AQ21" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AR21" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AS21" s="1" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AT21" s="1" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AU21" s="1" t="s">
         <v>50</v>
@@ -5079,28 +5208,28 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:49" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:49" ht="180" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>58</v>
@@ -5109,22 +5238,22 @@
         <v>58</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>495</v>
+        <v>220</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>494</v>
+        <v>222</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>50</v>
@@ -5142,7 +5271,7 @@
         <v>50</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>50</v>
@@ -5157,61 +5286,61 @@
         <v>50</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="AH22" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="AI22" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="AJ22" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AK22" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AL22" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="AN22" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="AO22" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="AP22" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="AQ22" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="AR22" s="1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="AS22" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="AT22" s="1" t="s">
         <v>50</v>
@@ -5226,15 +5355,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:49" ht="102" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:49" ht="135" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>53</v>
@@ -5243,7 +5372,7 @@
         <v>55</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1" t="s">
@@ -5256,11 +5385,10 @@
         <v>58</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="L23" s="1"/>
+        <v>240</v>
+      </c>
       <c r="M23" s="1" t="s">
-        <v>540</v>
+        <v>125</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>50</v>
@@ -5311,25 +5439,25 @@
         <v>50</v>
       </c>
       <c r="AD23" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="AH23" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="AI23" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="AJ23" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="AK23" s="1" t="s">
         <v>50</v>
@@ -5359,7 +5487,7 @@
         <v>50</v>
       </c>
       <c r="AT23" s="1" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="AU23" s="1" t="s">
         <v>50</v>
@@ -5371,24 +5499,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:49" ht="102" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:49" ht="135" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1" t="s">
@@ -5401,10 +5529,8 @@
         <v>58</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
+        <v>249</v>
+      </c>
       <c r="N24" s="9" t="s">
         <v>50</v>
       </c>
@@ -5454,10 +5580,10 @@
         <v>50</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AF24" s="1" t="s">
         <v>50</v>
@@ -5514,9 +5640,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:49" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -5525,54 +5651,127 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="5"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
-      <c r="Z25" s="5"/>
-      <c r="AA25" s="5"/>
-      <c r="AB25" s="5"/>
-      <c r="AC25" s="5"/>
-      <c r="AD25" s="5"/>
-      <c r="AE25" s="5"/>
-      <c r="AF25" s="5"/>
-      <c r="AG25" s="5"/>
-      <c r="AH25" s="5"/>
-      <c r="AI25" s="5"/>
-      <c r="AJ25" s="5"/>
-      <c r="AK25" s="5"/>
-      <c r="AL25" s="5"/>
-      <c r="AM25" s="5"/>
-      <c r="AN25" s="5"/>
-      <c r="AO25" s="5"/>
-      <c r="AP25" s="5"/>
-      <c r="AQ25" s="5"/>
-      <c r="AR25" s="5"/>
-      <c r="AS25" s="5"/>
-      <c r="AT25" s="5"/>
-      <c r="AU25" s="5"/>
-      <c r="AV25" s="5"/>
-      <c r="AW25" s="5"/>
+      <c r="I25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="W25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="X25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW25" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="26" spans="1:49" ht="72.900000000000006" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:49" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>53</v>
@@ -5581,10 +5780,10 @@
         <v>54</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1" t="s">
@@ -5597,109 +5796,109 @@
         <v>58</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="N26" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="AF26" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="AH26" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="AI26" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="AJ26" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AK26" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AL26" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AM26" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN26" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AO26" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AP26" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AQ26" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AR26" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AS26" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AT26" s="1" t="s">
         <v>50</v>
@@ -5714,12 +5913,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:49" ht="87.45" hidden="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:49" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>53</v>
@@ -5731,7 +5930,7 @@
         <v>55</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1" t="s">
@@ -5744,109 +5943,109 @@
         <v>58</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="N27" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="AC27" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AD27" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="AF27" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="AH27" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="AI27" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="AJ27" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="AK27" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="AL27" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="AN27" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="AP27" s="1" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="AQ27" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="AR27" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AS27" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="AT27" s="1" t="s">
         <v>50</v>
@@ -5861,12 +6060,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:49" ht="102" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:49" ht="105" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>53</v>
@@ -5875,10 +6074,10 @@
         <v>54</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1" t="s">
@@ -5891,31 +6090,31 @@
         <v>58</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>534</v>
+        <v>293</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>526</v>
+        <v>61</v>
       </c>
       <c r="N28" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="T28" s="1" t="s">
         <v>50</v>
@@ -5924,7 +6123,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>50</v>
@@ -5933,10 +6132,10 @@
         <v>50</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="AA28" s="1" t="s">
         <v>50</v>
@@ -5945,55 +6144,55 @@
         <v>50</v>
       </c>
       <c r="AC28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AD28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AF28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AH28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AI28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AJ28" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AL28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="AN28" s="1" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="AO28" s="1" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="AP28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AQ28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AR28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AS28" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="AT28" s="1" t="s">
         <v>50</v>
@@ -6008,12 +6207,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:49" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:49" ht="105" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>53</v>
@@ -6022,10 +6221,10 @@
         <v>54</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1" t="s">
@@ -6038,80 +6237,79 @@
         <v>58</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="L29" s="1"/>
+        <v>303</v>
+      </c>
       <c r="M29" s="1" t="s">
-        <v>530</v>
+        <v>304</v>
       </c>
       <c r="N29" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="AA29" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="AC29" s="1" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="AF29" s="1" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="AH29" s="1" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="AI29" s="1" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="AJ29" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="AK29" s="1" t="s">
         <v>50</v>
@@ -6129,13 +6327,13 @@
         <v>50</v>
       </c>
       <c r="AP29" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="AQ29" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="AR29" s="1" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="AS29" s="1" t="s">
         <v>50</v>
@@ -6153,12 +6351,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:49" ht="189.45" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>53</v>
@@ -6167,13 +6365,13 @@
         <v>54</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>57</v>
@@ -6185,113 +6383,112 @@
         <v>58</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="L30" s="1"/>
+        <v>316</v>
+      </c>
       <c r="M30" s="1" t="s">
-        <v>531</v>
+        <v>317</v>
       </c>
       <c r="N30" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AK30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AQ30" s="1" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="AR30" s="1" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="AS30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU30" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV30" s="1" t="s">
         <v>50</v>
@@ -6300,12 +6497,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:49" ht="218.6" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>53</v>
@@ -6314,14 +6511,14 @@
         <v>54</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>58</v>
@@ -6330,50 +6527,49 @@
         <v>58</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="L31" s="1"/>
+        <v>323</v>
+      </c>
       <c r="M31" s="1" t="s">
-        <v>532</v>
+        <v>324</v>
       </c>
       <c r="N31" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="P31" s="1" t="s">
         <v>50</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA31" s="1" t="s">
         <v>50</v>
@@ -6385,19 +6581,19 @@
         <v>50</v>
       </c>
       <c r="AD31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI31" s="1" t="s">
         <v>50</v>
@@ -6406,19 +6602,19 @@
         <v>50</v>
       </c>
       <c r="AK31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM31" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AN31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP31" s="1" t="s">
         <v>50</v>
@@ -6430,13 +6626,13 @@
         <v>50</v>
       </c>
       <c r="AS31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU31" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV31" s="1" t="s">
         <v>50</v>
@@ -6445,12 +6641,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:49" ht="233.15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:49" ht="120" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>53</v>
@@ -6459,14 +6655,14 @@
         <v>54</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>58</v>
@@ -6475,17 +6671,16 @@
         <v>58</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="L32" s="1"/>
+        <v>329</v>
+      </c>
       <c r="M32" s="1" t="s">
-        <v>533</v>
+        <v>330</v>
       </c>
       <c r="N32" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>50</v>
@@ -6494,16 +6689,16 @@
         <v>50</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V32" s="1" t="s">
         <v>50</v>
@@ -6512,40 +6707,40 @@
         <v>50</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y32" s="1" t="s">
         <v>50</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA32" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD32" s="1" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="AE32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF32" s="1" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="AG32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ32" s="1" t="s">
         <v>50</v>
@@ -6554,16 +6749,16 @@
         <v>50</v>
       </c>
       <c r="AL32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN32" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AO32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP32" s="1" t="s">
         <v>50</v>
@@ -6575,10 +6770,10 @@
         <v>50</v>
       </c>
       <c r="AS32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT32" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU32" s="1" t="s">
         <v>50</v>
@@ -6590,24 +6785,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:49" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:49" ht="120" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1" t="s">
@@ -6620,13 +6815,13 @@
         <v>58</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="N33" s="9" t="s">
         <v>50</v>
@@ -6653,7 +6848,7 @@
         <v>50</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>50</v>
@@ -6683,13 +6878,13 @@
         <v>50</v>
       </c>
       <c r="AF33" s="1" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="AG33" s="1" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="AH33" s="1" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="AI33" s="1" t="s">
         <v>50</v>
@@ -6698,10 +6893,10 @@
         <v>50</v>
       </c>
       <c r="AK33" s="1" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="AL33" s="1" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="AM33" s="1" t="s">
         <v>50</v>
@@ -6710,7 +6905,7 @@
         <v>50</v>
       </c>
       <c r="AO33" s="1" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="AP33" s="1" t="s">
         <v>50</v>
@@ -6737,28 +6932,28 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:49" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:49" ht="120" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="I34" s="13" t="s">
         <v>50</v>
@@ -6767,13 +6962,13 @@
         <v>58</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>525</v>
+        <v>347</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="N34" s="9" t="s">
         <v>50</v>
@@ -6800,7 +6995,7 @@
         <v>50</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>50</v>
@@ -6815,7 +7010,7 @@
         <v>50</v>
       </c>
       <c r="AA34" s="1" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="AB34" s="1" t="s">
         <v>50</v>
@@ -6833,22 +7028,22 @@
         <v>50</v>
       </c>
       <c r="AG34" s="1" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="AH34" s="1" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="AI34" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AJ34" s="1" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="AK34" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AL34" s="1" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="AM34" s="1" t="s">
         <v>50</v>
@@ -6857,16 +7052,16 @@
         <v>50</v>
       </c>
       <c r="AO34" s="1" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="AP34" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AQ34" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AR34" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AS34" s="1" t="s">
         <v>50</v>
@@ -6878,15 +7073,15 @@
         <v>50</v>
       </c>
       <c r="AV34" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AW34" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="35" spans="1:49" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -6895,54 +7090,127 @@
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
-      <c r="S35" s="5"/>
-      <c r="T35" s="5"/>
-      <c r="U35" s="5"/>
-      <c r="V35" s="5"/>
-      <c r="W35" s="5"/>
-      <c r="X35" s="5"/>
-      <c r="Y35" s="5"/>
-      <c r="Z35" s="5"/>
-      <c r="AA35" s="5"/>
-      <c r="AB35" s="5"/>
-      <c r="AC35" s="5"/>
-      <c r="AD35" s="5"/>
-      <c r="AE35" s="5"/>
-      <c r="AF35" s="5"/>
-      <c r="AG35" s="5"/>
-      <c r="AH35" s="5"/>
-      <c r="AI35" s="5"/>
-      <c r="AJ35" s="5"/>
-      <c r="AK35" s="5"/>
-      <c r="AL35" s="5"/>
-      <c r="AM35" s="5"/>
-      <c r="AN35" s="5"/>
-      <c r="AO35" s="5"/>
-      <c r="AP35" s="5"/>
-      <c r="AQ35" s="5"/>
-      <c r="AR35" s="5"/>
-      <c r="AS35" s="5"/>
-      <c r="AT35" s="5"/>
-      <c r="AU35" s="5"/>
-      <c r="AV35" s="5"/>
-      <c r="AW35" s="5"/>
+      <c r="I35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="W35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="X35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW35" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="36" spans="1:49" ht="116.6" hidden="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:49" ht="135" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>53</v>
@@ -6951,10 +7219,10 @@
         <v>54</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1" t="s">
@@ -6967,50 +7235,49 @@
         <v>58</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="L36" s="1"/>
+        <v>359</v>
+      </c>
       <c r="M36" s="1" t="s">
-        <v>501</v>
+        <v>360</v>
       </c>
       <c r="N36" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="AA36" s="1" t="s">
         <v>50</v>
@@ -7028,25 +7295,25 @@
         <v>50</v>
       </c>
       <c r="AF36" s="1" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="AG36" s="1" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="AH36" s="1" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="AI36" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AJ36" s="1" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="AK36" s="1" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="AL36" s="1" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="AM36" s="1" t="s">
         <v>50</v>
@@ -7055,22 +7322,22 @@
         <v>50</v>
       </c>
       <c r="AO36" s="1" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="AP36" s="1" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="AQ36" s="1" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="AR36" s="1" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="AS36" s="1" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="AT36" s="1" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="AU36" s="1" t="s">
         <v>50</v>
@@ -7082,24 +7349,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:49" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:49" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1" t="s">
@@ -7112,38 +7379,37 @@
         <v>58</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="L37" s="1"/>
+        <v>382</v>
+      </c>
       <c r="M37" s="1" t="s">
-        <v>504</v>
+        <v>383</v>
       </c>
       <c r="N37" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="P37" s="1" t="s">
         <v>50</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="T37" s="1" t="s">
         <v>50</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>50</v>
@@ -7173,25 +7439,25 @@
         <v>50</v>
       </c>
       <c r="AF37" s="1" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="AG37" s="1" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="AH37" s="1" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="AI37" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AJ37" s="1" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="AK37" s="1" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="AL37" s="1" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="AM37" s="1" t="s">
         <v>50</v>
@@ -7203,16 +7469,16 @@
         <v>50</v>
       </c>
       <c r="AP37" s="1" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="AQ37" s="1" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="AR37" s="1" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="AS37" s="1" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="AT37" s="1" t="s">
         <v>50</v>
@@ -7227,27 +7493,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:49" ht="66.45" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:49" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>57</v>
@@ -7259,17 +7525,16 @@
         <v>58</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="L38" s="1"/>
+        <v>399</v>
+      </c>
       <c r="M38" s="1" t="s">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="N38" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>50</v>
@@ -7281,13 +7546,13 @@
         <v>50</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="T38" s="1" t="s">
         <v>50</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="V38" s="1" t="s">
         <v>50</v>
@@ -7338,7 +7603,7 @@
         <v>50</v>
       </c>
       <c r="AL38" s="1" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="AM38" s="1" t="s">
         <v>50</v>
@@ -7350,7 +7615,7 @@
         <v>50</v>
       </c>
       <c r="AP38" s="1" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="AQ38" s="1" t="s">
         <v>50</v>
@@ -7359,7 +7624,7 @@
         <v>50</v>
       </c>
       <c r="AS38" s="1" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="AT38" s="1" t="s">
         <v>50</v>
@@ -7374,24 +7639,24 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:49" ht="44.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:49" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1" t="s">
@@ -7404,20 +7669,19 @@
         <v>58</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="L39" s="1"/>
+        <v>411</v>
+      </c>
       <c r="M39" s="1" t="s">
-        <v>506</v>
+        <v>412</v>
       </c>
       <c r="N39" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="Q39" s="1" t="s">
         <v>50</v>
@@ -7435,7 +7699,7 @@
         <v>50</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="W39" s="1" t="s">
         <v>50</v>
@@ -7465,7 +7729,7 @@
         <v>50</v>
       </c>
       <c r="AF39" s="1" t="s">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="AG39" s="1" t="s">
         <v>50</v>
@@ -7477,7 +7741,7 @@
         <v>50</v>
       </c>
       <c r="AJ39" s="1" t="s">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="AK39" s="1" t="s">
         <v>50</v>
@@ -7519,28 +7783,28 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:49" ht="54" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:49" ht="105" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="I40" s="13" t="s">
         <v>50</v>
@@ -7549,13 +7813,13 @@
         <v>58</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>508</v>
+        <v>422</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>518</v>
+        <v>423</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>509</v>
+        <v>424</v>
       </c>
       <c r="N40" s="9" t="s">
         <v>50</v>
@@ -7564,37 +7828,37 @@
         <v>50</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q40" s="1" t="s">
         <v>50</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W40" s="1" t="s">
         <v>50</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y40" s="1" t="s">
         <v>50</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA40" s="1" t="s">
         <v>50</v>
@@ -7609,16 +7873,16 @@
         <v>50</v>
       </c>
       <c r="AE40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF40" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AG40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI40" s="1" t="s">
         <v>50</v>
@@ -7630,7 +7894,7 @@
         <v>50</v>
       </c>
       <c r="AL40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM40" s="1" t="s">
         <v>50</v>
@@ -7639,54 +7903,54 @@
         <v>50</v>
       </c>
       <c r="AO40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AQ40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AR40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AS40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU40" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AV40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AW40" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="41" spans="1:49" ht="79.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>395</v>
+        <v>426</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>396</v>
+        <v>427</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>57</v>
@@ -7698,113 +7962,112 @@
         <v>58</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="L41" s="1"/>
+        <v>428</v>
+      </c>
       <c r="M41" s="1" t="s">
-        <v>511</v>
+        <v>429</v>
       </c>
       <c r="N41" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>50</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA41" s="1" t="s">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ41" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AK41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP41" s="1" t="s">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="AQ41" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AR41" s="1" t="s">
-        <v>399</v>
+        <v>432</v>
       </c>
       <c r="AS41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU41" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV41" s="1" t="s">
         <v>50</v>
@@ -7813,27 +8076,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:49" ht="58.3" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>401</v>
+        <v>434</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>402</v>
+        <v>435</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>57</v>
@@ -7845,113 +8108,112 @@
         <v>58</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="L42" s="1"/>
+        <v>428</v>
+      </c>
       <c r="M42" s="1" t="s">
-        <v>512</v>
+        <v>436</v>
       </c>
       <c r="N42" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA42" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ42" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AK42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP42" s="1" t="s">
-        <v>404</v>
+        <v>438</v>
       </c>
       <c r="AQ42" s="1" t="s">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="AR42" s="1" t="s">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="AS42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU42" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV42" s="1" t="s">
         <v>50</v>
@@ -7960,27 +8222,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:49" ht="93" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>407</v>
+        <v>441</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>57</v>
@@ -7992,115 +8254,115 @@
         <v>50</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>510</v>
+        <v>428</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>517</v>
+        <v>445</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>513</v>
+        <v>446</v>
       </c>
       <c r="N43" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>50</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AK43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP43" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AQ43" s="1" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="AR43" s="1" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="AS43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU43" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV43" s="1" t="s">
         <v>50</v>
@@ -8109,27 +8371,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:49" ht="93.9" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:49" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>57</v>
@@ -8141,115 +8403,115 @@
         <v>50</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>514</v>
+        <v>452</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>517</v>
+        <v>445</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>515</v>
+        <v>453</v>
       </c>
       <c r="N44" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>50</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AK44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP44" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AQ44" s="1" t="s">
-        <v>416</v>
+        <v>454</v>
       </c>
       <c r="AR44" s="1" t="s">
-        <v>417</v>
+        <v>455</v>
       </c>
       <c r="AS44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU44" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV44" s="1" t="s">
         <v>50</v>
@@ -8258,12 +8520,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:49" ht="95.6" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>418</v>
+        <v>456</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>419</v>
+        <v>457</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>53</v>
@@ -8272,13 +8534,13 @@
         <v>54</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>57</v>
@@ -8290,115 +8552,115 @@
         <v>50</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>510</v>
+        <v>428</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>517</v>
+        <v>445</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>516</v>
+        <v>459</v>
       </c>
       <c r="N45" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>50</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AK45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP45" s="1" t="s">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="AQ45" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AR45" s="1" t="s">
-        <v>422</v>
+        <v>461</v>
       </c>
       <c r="AS45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU45" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV45" s="1" t="s">
         <v>50</v>
@@ -8407,27 +8669,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:49" ht="78" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>423</v>
+        <v>462</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>424</v>
+        <v>463</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>425</v>
+        <v>464</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>57</v>
@@ -8439,144 +8701,144 @@
         <v>58</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>510</v>
+        <v>428</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>518</v>
+        <v>423</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>519</v>
+        <v>466</v>
       </c>
       <c r="N46" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA46" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AB46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ46" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AK46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AQ46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AR46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AS46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AW46" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="47" spans="1:49" ht="102" hidden="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:49" ht="90" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>427</v>
+        <v>467</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>429</v>
+        <v>469</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>57</v>
@@ -8587,133 +8849,133 @@
       <c r="J47" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="K47" s="21" t="s">
-        <v>510</v>
+      <c r="K47" s="1" t="s">
+        <v>428</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>518</v>
+        <v>423</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>520</v>
+        <v>471</v>
       </c>
       <c r="N47" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA47" s="1" t="s">
-        <v>431</v>
+        <v>472</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ47" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AK47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AQ47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AR47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AS47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AW47" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="48" spans="1:49" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:49" ht="105" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>432</v>
+        <v>473</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>433</v>
+        <v>474</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>53</v>
@@ -8722,13 +8984,13 @@
         <v>55</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I48" s="13" t="s">
         <v>50</v>
@@ -8737,126 +8999,126 @@
         <v>58</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>538</v>
+        <v>476</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>537</v>
+        <v>477</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>539</v>
+        <v>478</v>
       </c>
       <c r="N48" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA48" s="1" t="s">
-        <v>435</v>
+        <v>479</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ48" s="1" t="s">
-        <v>436</v>
+        <v>480</v>
       </c>
       <c r="AK48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AQ48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AR48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AS48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AW48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:49" ht="29.15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>437</v>
+        <v>481</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -8865,69 +9127,142 @@
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
-      <c r="R49" s="5"/>
-      <c r="S49" s="5"/>
-      <c r="T49" s="5"/>
-      <c r="U49" s="5"/>
-      <c r="V49" s="5"/>
-      <c r="W49" s="5"/>
-      <c r="X49" s="5"/>
-      <c r="Y49" s="5"/>
-      <c r="Z49" s="5"/>
-      <c r="AA49" s="5"/>
-      <c r="AB49" s="5"/>
-      <c r="AC49" s="5"/>
-      <c r="AD49" s="5"/>
-      <c r="AE49" s="5"/>
-      <c r="AF49" s="5"/>
-      <c r="AG49" s="5"/>
-      <c r="AH49" s="5"/>
-      <c r="AI49" s="5"/>
-      <c r="AJ49" s="5"/>
-      <c r="AK49" s="5"/>
-      <c r="AL49" s="5"/>
-      <c r="AM49" s="5"/>
-      <c r="AN49" s="5"/>
-      <c r="AO49" s="5"/>
-      <c r="AP49" s="5"/>
-      <c r="AQ49" s="5"/>
-      <c r="AR49" s="5"/>
-      <c r="AS49" s="5"/>
-      <c r="AT49" s="5"/>
-      <c r="AU49" s="5"/>
-      <c r="AV49" s="5"/>
-      <c r="AW49" s="5"/>
+      <c r="I49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="W49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="X49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW49" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="50" spans="1:49" ht="102" hidden="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:49" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>438</v>
+        <v>482</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>439</v>
+        <v>483</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>57</v>
@@ -8939,147 +9274,147 @@
         <v>58</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>521</v>
+        <v>485</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="N50" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA50" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AB50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ50" s="1" t="s">
-        <v>441</v>
+        <v>488</v>
       </c>
       <c r="AK50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AQ50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AR50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AS50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AW50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="51" spans="1:49" ht="131.15" hidden="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:49" ht="105" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>442</v>
+        <v>489</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>443</v>
+        <v>490</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>444</v>
+        <v>491</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I51" s="13" t="s">
         <v>50</v>
@@ -9088,126 +9423,126 @@
         <v>58</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>522</v>
+        <v>492</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>523</v>
+        <v>486</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>524</v>
+        <v>487</v>
       </c>
       <c r="N51" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="U51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="X51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Y51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AA51" s="1" t="s">
-        <v>445</v>
+        <v>493</v>
       </c>
       <c r="AB51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AC51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AE51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AF51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AG51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AI51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AJ51" s="1" t="s">
-        <v>446</v>
+        <v>494</v>
       </c>
       <c r="AK51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AL51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AM51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AN51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AO51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AP51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AQ51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AR51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AS51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AT51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AU51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AV51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AW51" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
-    <row r="52" spans="1:49" ht="43.75" hidden="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>447</v>
+        <v>495</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -9216,66 +9551,139 @@
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="5"/>
-      <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="5"/>
-      <c r="R52" s="5"/>
-      <c r="S52" s="5"/>
-      <c r="T52" s="5"/>
-      <c r="U52" s="5"/>
-      <c r="V52" s="5"/>
-      <c r="W52" s="5"/>
-      <c r="X52" s="5"/>
-      <c r="Y52" s="5"/>
-      <c r="Z52" s="5"/>
-      <c r="AA52" s="5"/>
-      <c r="AB52" s="5"/>
-      <c r="AC52" s="5"/>
-      <c r="AD52" s="5"/>
-      <c r="AE52" s="5"/>
-      <c r="AF52" s="5"/>
-      <c r="AG52" s="5"/>
-      <c r="AH52" s="5"/>
-      <c r="AI52" s="5"/>
-      <c r="AJ52" s="5"/>
-      <c r="AK52" s="5"/>
-      <c r="AL52" s="5"/>
-      <c r="AM52" s="5"/>
-      <c r="AN52" s="5"/>
-      <c r="AO52" s="5"/>
-      <c r="AP52" s="5"/>
-      <c r="AQ52" s="5"/>
-      <c r="AR52" s="5"/>
-      <c r="AS52" s="5"/>
-      <c r="AT52" s="5"/>
-      <c r="AU52" s="5"/>
-      <c r="AV52" s="5"/>
-      <c r="AW52" s="5"/>
+      <c r="I52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="T52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="W52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="X52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AR52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AS52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AU52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AV52" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW52" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="53" spans="1:49" ht="409.6" hidden="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:49" ht="240" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>448</v>
+        <v>496</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>449</v>
+        <v>497</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>55</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>450</v>
+        <v>498</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1" t="s">
@@ -9288,19 +9696,19 @@
         <v>58</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>451</v>
+        <v>499</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>453</v>
+        <v>501</v>
       </c>
       <c r="N53" s="9" t="s">
         <v>50</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>454</v>
+        <v>502</v>
       </c>
       <c r="P53" s="1" t="s">
         <v>50</v>
@@ -9312,107 +9720,100 @@
         <v>50</v>
       </c>
       <c r="S53" s="1" t="s">
-        <v>455</v>
+        <v>503</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>456</v>
+        <v>504</v>
       </c>
       <c r="U53" s="1" t="s">
-        <v>457</v>
+        <v>505</v>
       </c>
       <c r="V53" s="1" t="s">
-        <v>458</v>
+        <v>506</v>
       </c>
       <c r="W53" s="1" t="s">
         <v>50</v>
       </c>
       <c r="X53" s="1" t="s">
-        <v>459</v>
+        <v>507</v>
       </c>
       <c r="Y53" s="1" t="s">
         <v>50</v>
       </c>
       <c r="Z53" s="1" t="s">
-        <v>460</v>
+        <v>508</v>
       </c>
       <c r="AA53" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AB53" s="1" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="AC53" s="1" t="s">
-        <v>462</v>
+        <v>510</v>
       </c>
       <c r="AD53" s="1" t="s">
-        <v>463</v>
+        <v>511</v>
       </c>
       <c r="AE53" s="1" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="AF53" s="1" t="s">
-        <v>465</v>
+        <v>513</v>
       </c>
       <c r="AG53" s="1" t="s">
-        <v>466</v>
+        <v>514</v>
       </c>
       <c r="AH53" s="1" t="s">
-        <v>467</v>
+        <v>515</v>
       </c>
       <c r="AI53" s="1" t="s">
-        <v>468</v>
+        <v>516</v>
       </c>
       <c r="AJ53" s="1" t="s">
-        <v>469</v>
+        <v>517</v>
       </c>
       <c r="AK53" s="1" t="s">
-        <v>470</v>
+        <v>518</v>
       </c>
       <c r="AL53" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AM53" s="1" t="s">
-        <v>471</v>
+        <v>519</v>
       </c>
       <c r="AN53" s="1" t="s">
-        <v>472</v>
+        <v>520</v>
       </c>
       <c r="AO53" s="1" t="s">
-        <v>473</v>
+        <v>521</v>
       </c>
       <c r="AP53" s="1" t="s">
-        <v>474</v>
+        <v>522</v>
       </c>
       <c r="AQ53" s="1" t="s">
-        <v>475</v>
+        <v>523</v>
       </c>
       <c r="AR53" s="1" t="s">
-        <v>476</v>
+        <v>524</v>
       </c>
       <c r="AS53" s="1" t="s">
-        <v>477</v>
+        <v>525</v>
       </c>
       <c r="AT53" s="1" t="s">
-        <v>478</v>
+        <v>526</v>
       </c>
       <c r="AU53" s="1" t="s">
-        <v>479</v>
+        <v>527</v>
       </c>
       <c r="AV53" s="1" t="s">
-        <v>480</v>
+        <v>528</v>
       </c>
       <c r="AW53" s="1" t="s">
-        <v>481</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:M53" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="N/A"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9420,7 +9821,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -9428,104 +9829,104 @@
     <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>482</v>
+        <v>530</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>482</v>
+        <v>530</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>53</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>483</v>
+        <v>531</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>484</v>
+        <v>532</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>485</v>
+        <v>533</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>486</v>
+        <v>534</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>487</v>
+        <v>535</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>488</v>
+        <v>536</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="C5" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>490</v>
+        <v>538</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>491</v>
+        <v>539</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>58</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>492</v>
+        <v>540</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>50</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>493</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
